--- a/EL MIRADOR/Octubre/Octubre - EL MIRADOR  (1).xlsx
+++ b/EL MIRADOR/Octubre/Octubre - EL MIRADOR  (1).xlsx
@@ -5,29 +5,34 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\EL MIRADOR\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\EL MIRADOR\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08D37EBA-EBFA-4ED0-B195-450ECDF3158F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FA6DB7-6E57-4435-AB19-4FFAEF69F1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
     <sheet name="ANOTACIONES" sheetId="3" r:id="rId3"/>
-    <sheet name="Hoja1" sheetId="4" r:id="rId4"/>
+    <sheet name="SUELDOS" sheetId="5" r:id="rId4"/>
+    <sheet name="Hoja1" sheetId="4" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$155</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$159</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">SUELDOS!$A$3:$J$28</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="361">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1110,6 +1115,15 @@
   </si>
   <si>
     <t>la uf 55 habia abonado el 14 de oct 235.000,55, NO la pusimos paga, revisar eso y en el banco esta marcada como que la pusimos (sin embargo en el excel no fue asi)</t>
+  </si>
+  <si>
+    <t>Firma</t>
+  </si>
+  <si>
+    <t>__________________________________</t>
+  </si>
+  <si>
+    <t>Aclaracion</t>
   </si>
 </sst>
 </file>
@@ -1711,7 +1725,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="287">
+  <cellXfs count="300">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2041,14 +2055,26 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2128,19 +2154,34 @@
     <xf numFmtId="1" fontId="19" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2277,6 +2318,39 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="RESUMEN"/>
+      <sheetName val="PRORRATEO"/>
+      <sheetName val="ANOTACIONES"/>
+      <sheetName val="SUELDOS"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="22">
+          <cell r="A22" t="str">
+            <v xml:space="preserve">Sueldo encargada Sonia Arzamendia Galeano </v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>Sueldo encargada Miriam</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2567,24 +2641,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R169"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="6" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="118"/>
       <c r="B1" s="127"/>
       <c r="C1" s="137" t="s">
@@ -2598,7 +2672,7 @@
       <c r="I1" s="116"/>
       <c r="J1" s="117"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="119"/>
       <c r="B2" s="128"/>
       <c r="C2" s="128" t="s">
@@ -2612,7 +2686,7 @@
       <c r="I2" s="129"/>
       <c r="J2" s="115"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="119"/>
       <c r="B3" s="128"/>
       <c r="C3" s="128" t="s">
@@ -2628,7 +2702,7 @@
       <c r="I3" s="129"/>
       <c r="J3" s="115"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="119"/>
       <c r="B4" s="128"/>
       <c r="C4" s="128" t="s">
@@ -2642,7 +2716,7 @@
       <c r="I4" s="129"/>
       <c r="J4" s="115"/>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="123"/>
       <c r="B5" s="128"/>
       <c r="C5" s="128" t="s">
@@ -2658,7 +2732,7 @@
       <c r="I5" s="128"/>
       <c r="J5" s="124"/>
     </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="123"/>
       <c r="B6" s="128"/>
       <c r="C6" s="128" t="s">
@@ -2672,7 +2746,7 @@
       <c r="I6" s="128"/>
       <c r="J6" s="124"/>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="125"/>
       <c r="B7" s="126"/>
       <c r="C7" s="126"/>
@@ -2684,11 +2758,11 @@
       <c r="I7" s="126"/>
       <c r="J7" s="130"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="241" t="s">
         <v>265</v>
       </c>
@@ -2702,7 +2776,7 @@
       <c r="I14" s="241"/>
       <c r="J14" s="241"/>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="241"/>
       <c r="B15" s="241"/>
       <c r="C15" s="241"/>
@@ -2714,7 +2788,7 @@
       <c r="I15" s="241"/>
       <c r="J15" s="241"/>
     </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="241"/>
       <c r="B16" s="241"/>
       <c r="C16" s="241"/>
@@ -2726,7 +2800,7 @@
       <c r="I16" s="241"/>
       <c r="J16" s="241"/>
     </row>
-    <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="241"/>
       <c r="B17" s="241"/>
       <c r="C17" s="241"/>
@@ -2738,7 +2812,7 @@
       <c r="I17" s="241"/>
       <c r="J17" s="241"/>
     </row>
-    <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="241"/>
       <c r="B18" s="241"/>
       <c r="C18" s="241"/>
@@ -2750,11 +2824,11 @@
       <c r="I18" s="241"/>
       <c r="J18" s="241"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="H19" s="100"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="250" t="s">
         <v>328</v>
       </c>
@@ -2768,7 +2842,7 @@
       <c r="I20" s="250"/>
       <c r="J20" s="250"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="250"/>
       <c r="B21" s="250"/>
       <c r="C21" s="250"/>
@@ -2780,7 +2854,7 @@
       <c r="I21" s="250"/>
       <c r="J21" s="250"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="250"/>
       <c r="B22" s="250"/>
       <c r="C22" s="250"/>
@@ -2792,10 +2866,10 @@
       <c r="I22" s="250"/>
       <c r="J22" s="250"/>
     </row>
-    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="100"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>19</v>
       </c>
@@ -2821,7 +2895,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="50" t="s">
         <v>238</v>
       </c>
@@ -2835,7 +2909,7 @@
       <c r="I25" s="101"/>
       <c r="J25" s="101"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>45</v>
       </c>
@@ -2851,7 +2925,7 @@
       <c r="I26" s="58"/>
       <c r="J26" s="58"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>241</v>
       </c>
@@ -2867,7 +2941,7 @@
       <c r="I27" s="58"/>
       <c r="J27" s="58"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>239</v>
       </c>
@@ -2884,7 +2958,7 @@
       <c r="I28" s="58"/>
       <c r="J28" s="58"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>240</v>
       </c>
@@ -2900,7 +2974,7 @@
       <c r="I29" s="58"/>
       <c r="J29" s="58"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>316</v>
       </c>
@@ -2916,7 +2990,7 @@
       <c r="I30" s="58"/>
       <c r="J30" s="58"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>242</v>
       </c>
@@ -2932,7 +3006,7 @@
       <c r="I31" s="58"/>
       <c r="J31" s="58"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="99" t="s">
         <v>171</v>
       </c>
@@ -2949,7 +3023,7 @@
       <c r="I32" s="98"/>
       <c r="J32" s="98"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="50" t="s">
         <v>237</v>
       </c>
@@ -2963,7 +3037,7 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>45</v>
       </c>
@@ -2979,7 +3053,7 @@
       <c r="I34" s="58"/>
       <c r="J34" s="58"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>312</v>
       </c>
@@ -2993,7 +3067,7 @@
       <c r="I35" s="58"/>
       <c r="J35" s="58"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>241</v>
       </c>
@@ -3010,7 +3084,7 @@
       <c r="I36" s="58"/>
       <c r="J36" s="58"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>239</v>
       </c>
@@ -3027,7 +3101,7 @@
       <c r="I37" s="58"/>
       <c r="J37" s="58"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>240</v>
       </c>
@@ -3044,7 +3118,7 @@
       <c r="I38" s="58"/>
       <c r="J38" s="58"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>316</v>
       </c>
@@ -3061,7 +3135,7 @@
       <c r="I39" s="58"/>
       <c r="J39" s="58"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>242</v>
       </c>
@@ -3077,7 +3151,7 @@
       <c r="I40" s="58"/>
       <c r="J40" s="58"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="99" t="s">
         <v>171</v>
       </c>
@@ -3094,7 +3168,7 @@
       <c r="I41" s="98"/>
       <c r="J41" s="98"/>
     </row>
-    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33" t="s">
         <v>1</v>
       </c>
@@ -3137,7 +3211,7 @@
         <v>1522551.4</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="32" t="s">
         <v>34</v>
       </c>
@@ -3160,7 +3234,7 @@
       </c>
       <c r="L43" s="69"/>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="32"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -3181,7 +3255,7 @@
       </c>
       <c r="L44" s="69"/>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="32"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -3194,7 +3268,7 @@
       <c r="J45" s="6"/>
       <c r="L45" s="69"/>
     </row>
-    <row r="46" spans="1:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="32"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -3207,7 +3281,7 @@
       <c r="J46" s="6"/>
       <c r="L46" s="69"/>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33" t="s">
         <v>40</v>
       </c>
@@ -3238,7 +3312,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="32" t="s">
         <v>253</v>
       </c>
@@ -3259,7 +3333,7 @@
       </c>
       <c r="L48" s="69"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -3275,7 +3349,7 @@
       <c r="J49" s="58"/>
       <c r="L49" s="69"/>
     </row>
-    <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -3291,7 +3365,7 @@
       <c r="J50" s="58"/>
       <c r="L50" s="69"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="32"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -3310,7 +3384,7 @@
       </c>
       <c r="L51" s="69"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="33" t="s">
         <v>35</v>
       </c>
@@ -3338,7 +3412,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="32" t="s">
         <v>247</v>
       </c>
@@ -3353,7 +3427,7 @@
       <c r="J53" s="49"/>
       <c r="L53" s="69"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="35" t="s">
         <v>250</v>
       </c>
@@ -3368,7 +3442,7 @@
       <c r="J54" s="49"/>
       <c r="L54" s="69"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="35" t="s">
         <v>252</v>
       </c>
@@ -3383,7 +3457,7 @@
       <c r="J55" s="49"/>
       <c r="L55" s="69"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="35" t="s">
         <v>251</v>
       </c>
@@ -3398,7 +3472,7 @@
       <c r="J56" s="49"/>
       <c r="L56" s="69"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="33" t="s">
         <v>249</v>
       </c>
@@ -3441,7 +3515,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="32" t="s">
         <v>2</v>
       </c>
@@ -3456,7 +3530,7 @@
       <c r="J58" s="6"/>
       <c r="L58" s="69"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>243</v>
       </c>
@@ -3475,7 +3549,7 @@
       <c r="J59" s="6"/>
       <c r="L59" s="69"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>297</v>
       </c>
@@ -3494,7 +3568,7 @@
       <c r="J60" s="6"/>
       <c r="L60" s="69"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="33" t="s">
         <v>248</v>
       </c>
@@ -3537,7 +3611,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="32" t="s">
         <v>230</v>
       </c>
@@ -3552,7 +3626,7 @@
       <c r="J62" s="36"/>
       <c r="L62" s="69"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>234</v>
       </c>
@@ -3593,7 +3667,7 @@
       </c>
       <c r="L63" s="69"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>235</v>
       </c>
@@ -3634,7 +3708,7 @@
       </c>
       <c r="L64" s="69"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>236</v>
       </c>
@@ -3675,7 +3749,7 @@
       </c>
       <c r="L65" s="69"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="33" t="s">
         <v>3</v>
       </c>
@@ -3718,7 +3792,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="32" t="s">
         <v>4</v>
       </c>
@@ -3733,7 +3807,7 @@
       <c r="J67" s="6"/>
       <c r="L67" s="69"/>
     </row>
-    <row r="68" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="71" t="s">
         <v>244</v>
       </c>
@@ -3785,7 +3859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="71" t="s">
         <v>244</v>
       </c>
@@ -3831,7 +3905,7 @@
       <c r="M69" s="86"/>
       <c r="N69" s="86"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>245</v>
       </c>
@@ -3877,7 +3951,7 @@
       <c r="M70" s="86"/>
       <c r="N70" s="86"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>245</v>
       </c>
@@ -3923,7 +3997,7 @@
       <c r="M71" s="86"/>
       <c r="N71" s="86"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>246</v>
       </c>
@@ -3961,7 +4035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>330</v>
       </c>
@@ -3992,7 +4066,7 @@
       <c r="M73" s="86"/>
       <c r="N73" s="86"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="35" t="s">
         <v>300</v>
       </c>
@@ -4029,7 +4103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="35" t="s">
         <v>282</v>
       </c>
@@ -4081,7 +4155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="35" t="s">
         <v>282</v>
       </c>
@@ -4133,7 +4207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="35" t="s">
         <v>283</v>
       </c>
@@ -4185,7 +4259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="35" t="s">
         <v>283</v>
       </c>
@@ -4234,7 +4308,7 @@
       </c>
       <c r="N78" s="86"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="35" t="s">
         <v>283</v>
       </c>
@@ -4286,7 +4360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="156" t="s">
         <v>281</v>
       </c>
@@ -4319,7 +4393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="156"/>
       <c r="B81" s="154"/>
       <c r="C81" s="154"/>
@@ -4344,7 +4418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="248"/>
       <c r="B82" s="249"/>
       <c r="C82" s="251"/>
@@ -4369,7 +4443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="248"/>
       <c r="B83" s="249"/>
       <c r="C83" s="251"/>
@@ -4394,7 +4468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="152"/>
       <c r="B84" s="153"/>
       <c r="C84" s="84"/>
@@ -4419,7 +4493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="144"/>
       <c r="B85" s="144"/>
       <c r="C85" s="155"/>
@@ -4447,7 +4521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="71"/>
       <c r="B86" s="72"/>
       <c r="C86" s="72"/>
@@ -4465,7 +4539,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="33" t="s">
         <v>5</v>
       </c>
@@ -4512,7 +4586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -4525,7 +4599,7 @@
       <c r="J88" s="6"/>
       <c r="L88" s="69"/>
     </row>
-    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -4538,7 +4612,7 @@
       <c r="J89" s="6"/>
       <c r="L89" s="69"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="32" t="s">
         <v>231</v>
       </c>
@@ -4553,7 +4627,7 @@
       <c r="J90" s="6"/>
       <c r="L90" s="69"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
         <v>331</v>
       </c>
@@ -4591,7 +4665,7 @@
       <c r="K91" s="74"/>
       <c r="L91" s="69"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="35"/>
       <c r="C92" s="6"/>
@@ -4608,7 +4682,7 @@
       <c r="K92" s="74"/>
       <c r="L92" s="69"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="35"/>
       <c r="C93" s="6"/>
@@ -4622,7 +4696,7 @@
       <c r="K93" s="74"/>
       <c r="L93" s="69"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="35"/>
       <c r="C94" s="6"/>
@@ -4636,7 +4710,7 @@
       <c r="K94" s="74"/>
       <c r="L94" s="69"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="35"/>
       <c r="C95" s="6"/>
@@ -4650,7 +4724,7 @@
       <c r="K95" s="74"/>
       <c r="L95" s="69"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -4664,7 +4738,7 @@
       <c r="L96" s="69"/>
       <c r="M96" s="43"/>
     </row>
-    <row r="97" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="33" t="s">
         <v>232</v>
       </c>
@@ -4708,7 +4782,7 @@
       </c>
       <c r="N97" s="43"/>
     </row>
-    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -4721,7 +4795,7 @@
       <c r="J98" s="6"/>
       <c r="L98" s="69"/>
     </row>
-    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -4734,7 +4808,7 @@
       <c r="J99" s="6"/>
       <c r="L99" s="69"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="32" t="s">
         <v>6</v>
       </c>
@@ -4749,7 +4823,7 @@
       <c r="J100" s="6"/>
       <c r="L100" s="69"/>
     </row>
-    <row r="101" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
         <v>7</v>
       </c>
@@ -4788,7 +4862,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="32"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -4802,7 +4876,7 @@
       <c r="L102" s="69"/>
       <c r="N102" s="44"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -4816,7 +4890,7 @@
       <c r="L103" s="69"/>
       <c r="N103" s="43"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="33" t="s">
         <v>8</v>
       </c>
@@ -4860,7 +4934,7 @@
       </c>
       <c r="N104" s="43"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
         <v>28</v>
       </c>
@@ -4895,7 +4969,7 @@
       </c>
       <c r="L105" s="69"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
         <v>29</v>
       </c>
@@ -4928,7 +5002,7 @@
       </c>
       <c r="L106" s="69"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="33" t="s">
         <v>233</v>
       </c>
@@ -4971,7 +5045,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="104"/>
       <c r="B108" s="104"/>
       <c r="C108" s="104"/>
@@ -4984,7 +5058,7 @@
       <c r="J108" s="104"/>
       <c r="L108" s="69"/>
     </row>
-    <row r="109" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="106" t="s">
         <v>46</v>
       </c>
@@ -5027,7 +5101,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="109"/>
       <c r="B110" s="110"/>
       <c r="C110" s="110"/>
@@ -5041,7 +5115,7 @@
       <c r="K110" s="43"/>
       <c r="L110" s="69"/>
     </row>
-    <row r="111" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
         <v>30</v>
       </c>
@@ -5088,7 +5162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D112" s="89"/>
       <c r="E112" s="43"/>
       <c r="F112" s="43"/>
@@ -5096,7 +5170,7 @@
       <c r="H112" s="43"/>
       <c r="I112" s="43"/>
     </row>
-    <row r="113" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="64" t="s">
         <v>41</v>
       </c>
@@ -5108,7 +5182,7 @@
       <c r="H113" s="43"/>
       <c r="I113" s="43"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>343</v>
       </c>
@@ -5121,7 +5195,7 @@
       <c r="H114" s="43"/>
       <c r="I114" s="43"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>344</v>
       </c>
@@ -5134,7 +5208,7 @@
       <c r="H115" s="43"/>
       <c r="I115" s="43"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>345</v>
       </c>
@@ -5147,7 +5221,7 @@
       <c r="H116" s="43"/>
       <c r="I116" s="43"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>346</v>
       </c>
@@ -5160,7 +5234,7 @@
       <c r="H117" s="43"/>
       <c r="I117" s="43"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>347</v>
       </c>
@@ -5173,7 +5247,7 @@
       <c r="H118" s="43"/>
       <c r="I118" s="43"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>348</v>
       </c>
@@ -5186,7 +5260,7 @@
       <c r="H119" s="43"/>
       <c r="I119" s="43"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>349</v>
       </c>
@@ -5199,7 +5273,7 @@
       <c r="H120" s="43"/>
       <c r="I120" s="43"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>352</v>
       </c>
@@ -5212,7 +5286,7 @@
       <c r="H121" s="43"/>
       <c r="I121" s="43"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>351</v>
       </c>
@@ -5226,7 +5300,7 @@
       <c r="H122" s="43"/>
       <c r="I122" s="43"/>
     </row>
-    <row r="123" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>350</v>
       </c>
@@ -5240,7 +5314,7 @@
       <c r="H123" s="43"/>
       <c r="I123" s="43"/>
     </row>
-    <row r="124" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="65" t="s">
         <v>17</v>
       </c>
@@ -5255,21 +5329,21 @@
       <c r="H124" s="43"/>
       <c r="I124" s="43"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E125" s="43"/>
       <c r="F125" s="43"/>
       <c r="G125" s="43"/>
       <c r="H125" s="43"/>
       <c r="I125" s="43"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E126" s="60"/>
       <c r="F126" s="60"/>
       <c r="G126" s="60"/>
       <c r="H126" s="60"/>
       <c r="I126" s="60"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="246" t="s">
         <v>36</v>
       </c>
@@ -5295,7 +5369,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="248"/>
       <c r="B128" s="249"/>
       <c r="C128" s="84"/>
@@ -5310,7 +5384,7 @@
       <c r="I128" s="68"/>
       <c r="J128" s="58"/>
     </row>
-    <row r="129" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="248"/>
       <c r="B129" s="249"/>
       <c r="C129" s="84"/>
@@ -5322,7 +5396,7 @@
       <c r="I129" s="68"/>
       <c r="J129" s="58"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="243" t="s">
         <v>17</v>
       </c>
@@ -5353,14 +5427,14 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E132" s="43"/>
       <c r="F132" s="43"/>
       <c r="G132" s="43"/>
       <c r="H132" s="43"/>
       <c r="I132" s="43"/>
     </row>
-    <row r="133" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="38" t="s">
         <v>31</v>
       </c>
@@ -5369,7 +5443,7 @@
         <v>11000000</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="40" t="s">
         <v>33</v>
       </c>
@@ -5386,7 +5460,7 @@
       <c r="H134" s="252"/>
       <c r="I134" s="252"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D135" s="252"/>
       <c r="E135" s="252"/>
       <c r="F135" s="252"/>
@@ -5394,7 +5468,7 @@
       <c r="H135" s="252"/>
       <c r="I135" s="252"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="16" t="s">
         <v>20</v>
       </c>
@@ -5407,7 +5481,7 @@
       <c r="H136" s="252"/>
       <c r="I136" s="252"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="19" t="s">
         <v>21</v>
       </c>
@@ -5422,7 +5496,7 @@
       <c r="H137" s="252"/>
       <c r="I137" s="252"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="21" t="s">
         <v>22</v>
       </c>
@@ -5440,7 +5514,7 @@
       <c r="H138" s="252"/>
       <c r="I138" s="252"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="21" t="s">
         <v>38</v>
       </c>
@@ -5457,7 +5531,7 @@
       <c r="I139" s="252"/>
       <c r="K139" s="44"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="21" t="s">
         <v>37</v>
       </c>
@@ -5474,7 +5548,7 @@
       <c r="I140" s="252"/>
       <c r="K140" s="52"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="21" t="s">
         <v>311</v>
       </c>
@@ -5491,7 +5565,7 @@
       <c r="I141" s="252"/>
       <c r="K141" s="52"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="21" t="s">
         <v>32</v>
       </c>
@@ -5507,7 +5581,7 @@
       <c r="H142" s="252"/>
       <c r="I142" s="252"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="21" t="s">
         <v>309</v>
       </c>
@@ -5522,7 +5596,7 @@
       <c r="H143" s="252"/>
       <c r="I143" s="252"/>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="21" t="s">
         <v>41</v>
       </c>
@@ -5538,7 +5612,7 @@
       <c r="H144" s="252"/>
       <c r="I144" s="252"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="21" t="s">
         <v>342</v>
       </c>
@@ -5553,7 +5627,7 @@
       <c r="H145" s="252"/>
       <c r="I145" s="252"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="19" t="s">
         <v>24</v>
       </c>
@@ -5569,7 +5643,7 @@
       <c r="H146" s="252"/>
       <c r="I146" s="252"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="22"/>
       <c r="C147" s="18"/>
       <c r="D147" s="252"/>
@@ -5579,7 +5653,7 @@
       <c r="H147" s="252"/>
       <c r="I147" s="252"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="16" t="s">
         <v>310</v>
       </c>
@@ -5592,19 +5666,19 @@
       <c r="H148" s="252"/>
       <c r="I148" s="252"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="19"/>
       <c r="B149" s="31"/>
       <c r="C149" s="18"/>
       <c r="D149" s="25"/>
     </row>
-    <row r="150" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="179"/>
       <c r="B150" s="30"/>
       <c r="C150" s="18"/>
       <c r="D150" s="25"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="36" t="s">
         <v>17</v>
       </c>
@@ -5615,17 +5689,17 @@
       <c r="C151" s="18"/>
       <c r="D151" s="25"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="22"/>
       <c r="C152" s="18"/>
       <c r="D152" s="25"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="22"/>
       <c r="C153" s="18"/>
       <c r="D153" s="25"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C154" s="18"/>
       <c r="D154" s="43"/>
       <c r="E154" s="86"/>
@@ -5634,7 +5708,7 @@
       <c r="H154" s="86"/>
       <c r="I154" s="86"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="16" t="s">
         <v>25</v>
       </c>
@@ -5650,7 +5724,7 @@
       <c r="I155" s="86"/>
       <c r="J155" s="86"/>
     </row>
-    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="19" t="s">
         <v>260</v>
       </c>
@@ -5663,7 +5737,7 @@
       <c r="H156" s="93"/>
       <c r="I156" s="93"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="19"/>
       <c r="B157" s="85"/>
       <c r="C157" s="24"/>
@@ -5673,7 +5747,7 @@
       <c r="H157" s="43"/>
       <c r="I157" s="43"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="36" t="s">
         <v>17</v>
       </c>
@@ -5683,18 +5757,18 @@
       </c>
       <c r="C158" s="24"/>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C159" s="25"/>
       <c r="D159" s="86"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B160" s="22"/>
       <c r="C160" s="18"/>
     </row>
-    <row r="162" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:18" x14ac:dyDescent="0.3">
       <c r="R162" s="9"/>
     </row>
-    <row r="165" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B165" s="242"/>
       <c r="C165" s="242"/>
       <c r="D165" s="242"/>
@@ -5704,7 +5778,7 @@
       <c r="H165" s="95"/>
       <c r="I165" s="95"/>
     </row>
-    <row r="166" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B166" s="242"/>
       <c r="C166" s="242"/>
       <c r="D166" s="242"/>
@@ -5714,7 +5788,7 @@
       <c r="H166" s="95"/>
       <c r="I166" s="95"/>
     </row>
-    <row r="167" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B167" s="242"/>
       <c r="C167" s="242"/>
       <c r="D167" s="242"/>
@@ -5724,7 +5798,7 @@
       <c r="H167" s="95"/>
       <c r="I167" s="95"/>
     </row>
-    <row r="168" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B168" s="242"/>
       <c r="C168" s="242"/>
       <c r="D168" s="242"/>
@@ -5734,7 +5808,7 @@
       <c r="H168" s="95"/>
       <c r="I168" s="95"/>
     </row>
-    <row r="169" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B169" s="242"/>
       <c r="C169" s="242"/>
       <c r="D169" s="242"/>
@@ -5766,27 +5840,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DI154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="36.42578125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" customWidth="1"/>
+    <col min="5" max="5" width="36.44140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="180"/>
       <c r="B1" s="181"/>
       <c r="C1" s="181"/>
@@ -5802,15 +5876,15 @@
       <c r="K1" s="181" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="258">
+      <c r="L1" s="262">
         <f>RESUMEN!D111-RESUMEN!D109</f>
         <v>9608383.8599999994</v>
       </c>
-      <c r="M1" s="259"/>
+      <c r="M1" s="263"/>
       <c r="N1" s="182"/>
       <c r="O1" s="59"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="183"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -5833,7 +5907,7 @@
       <c r="N2" s="185"/>
       <c r="O2" s="59"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="183" t="str">
         <f>RESUMEN!C5</f>
         <v>PERÍODO: OCTUBRE</v>
@@ -5855,7 +5929,7 @@
       <c r="N3" s="188"/>
       <c r="O3" s="15"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="189"/>
       <c r="B4" s="190"/>
       <c r="C4" s="190"/>
@@ -5872,188 +5946,188 @@
       <c r="N4" s="193"/>
       <c r="O4" s="15"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="271" t="s">
         <v>337</v>
       </c>
-      <c r="D5" s="268"/>
-      <c r="E5" s="268"/>
-      <c r="F5" s="268"/>
-      <c r="G5" s="268"/>
-      <c r="H5" s="268"/>
-      <c r="I5" s="268"/>
-      <c r="J5" s="268"/>
-      <c r="K5" s="268"/>
-      <c r="L5" s="268"/>
-      <c r="M5" s="268"/>
-      <c r="N5" s="269"/>
+      <c r="D5" s="272"/>
+      <c r="E5" s="272"/>
+      <c r="F5" s="272"/>
+      <c r="G5" s="272"/>
+      <c r="H5" s="272"/>
+      <c r="I5" s="272"/>
+      <c r="J5" s="272"/>
+      <c r="K5" s="272"/>
+      <c r="L5" s="272"/>
+      <c r="M5" s="272"/>
+      <c r="N5" s="273"/>
       <c r="O5" s="15"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="270"/>
-      <c r="D6" s="271"/>
-      <c r="E6" s="271"/>
-      <c r="F6" s="271"/>
-      <c r="G6" s="271"/>
-      <c r="H6" s="271"/>
-      <c r="I6" s="271"/>
-      <c r="J6" s="271"/>
-      <c r="K6" s="271"/>
-      <c r="L6" s="271"/>
-      <c r="M6" s="271"/>
-      <c r="N6" s="272"/>
+      <c r="C6" s="274"/>
+      <c r="D6" s="275"/>
+      <c r="E6" s="275"/>
+      <c r="F6" s="275"/>
+      <c r="G6" s="275"/>
+      <c r="H6" s="275"/>
+      <c r="I6" s="275"/>
+      <c r="J6" s="275"/>
+      <c r="K6" s="275"/>
+      <c r="L6" s="275"/>
+      <c r="M6" s="275"/>
+      <c r="N6" s="276"/>
       <c r="O6" s="15"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="270"/>
-      <c r="D7" s="271"/>
-      <c r="E7" s="271"/>
-      <c r="F7" s="271"/>
-      <c r="G7" s="271"/>
-      <c r="H7" s="271"/>
-      <c r="I7" s="271"/>
-      <c r="J7" s="271"/>
-      <c r="K7" s="271"/>
-      <c r="L7" s="271"/>
-      <c r="M7" s="271"/>
-      <c r="N7" s="272"/>
+      <c r="C7" s="274"/>
+      <c r="D7" s="275"/>
+      <c r="E7" s="275"/>
+      <c r="F7" s="275"/>
+      <c r="G7" s="275"/>
+      <c r="H7" s="275"/>
+      <c r="I7" s="275"/>
+      <c r="J7" s="275"/>
+      <c r="K7" s="275"/>
+      <c r="L7" s="275"/>
+      <c r="M7" s="275"/>
+      <c r="N7" s="276"/>
       <c r="O7" s="15"/>
     </row>
-    <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="273"/>
-      <c r="D8" s="274"/>
-      <c r="E8" s="274"/>
-      <c r="F8" s="274"/>
-      <c r="G8" s="274"/>
-      <c r="H8" s="274"/>
-      <c r="I8" s="274"/>
-      <c r="J8" s="274"/>
-      <c r="K8" s="274"/>
-      <c r="L8" s="274"/>
-      <c r="M8" s="274"/>
-      <c r="N8" s="275"/>
+      <c r="C8" s="277"/>
+      <c r="D8" s="278"/>
+      <c r="E8" s="278"/>
+      <c r="F8" s="278"/>
+      <c r="G8" s="278"/>
+      <c r="H8" s="278"/>
+      <c r="I8" s="278"/>
+      <c r="J8" s="278"/>
+      <c r="K8" s="278"/>
+      <c r="L8" s="278"/>
+      <c r="M8" s="278"/>
+      <c r="N8" s="279"/>
       <c r="P8" s="86">
         <f>L1-K133</f>
         <v>-1338773.6948400009</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="276" t="s">
+      <c r="C9" s="280" t="s">
         <v>355</v>
       </c>
-      <c r="D9" s="277"/>
-      <c r="E9" s="277"/>
-      <c r="F9" s="277"/>
-      <c r="G9" s="277"/>
-      <c r="H9" s="277"/>
-      <c r="I9" s="277"/>
-      <c r="J9" s="277"/>
-      <c r="K9" s="277"/>
-      <c r="L9" s="277"/>
-      <c r="M9" s="277"/>
-      <c r="N9" s="278"/>
+      <c r="D9" s="281"/>
+      <c r="E9" s="281"/>
+      <c r="F9" s="281"/>
+      <c r="G9" s="281"/>
+      <c r="H9" s="281"/>
+      <c r="I9" s="281"/>
+      <c r="J9" s="281"/>
+      <c r="K9" s="281"/>
+      <c r="L9" s="281"/>
+      <c r="M9" s="281"/>
+      <c r="N9" s="282"/>
       <c r="P9" s="86"/>
     </row>
-    <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="279"/>
-      <c r="D10" s="280"/>
-      <c r="E10" s="280"/>
-      <c r="F10" s="280"/>
-      <c r="G10" s="280"/>
-      <c r="H10" s="280"/>
-      <c r="I10" s="280"/>
-      <c r="J10" s="280"/>
-      <c r="K10" s="280"/>
-      <c r="L10" s="280"/>
-      <c r="M10" s="280"/>
-      <c r="N10" s="281"/>
+      <c r="C10" s="283"/>
+      <c r="D10" s="284"/>
+      <c r="E10" s="284"/>
+      <c r="F10" s="284"/>
+      <c r="G10" s="284"/>
+      <c r="H10" s="284"/>
+      <c r="I10" s="284"/>
+      <c r="J10" s="284"/>
+      <c r="K10" s="284"/>
+      <c r="L10" s="284"/>
+      <c r="M10" s="284"/>
+      <c r="N10" s="285"/>
       <c r="P10" s="86"/>
     </row>
-    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="254" t="s">
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="253" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="282" t="s">
+      <c r="B11" s="255" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="254" t="s">
+      <c r="C11" s="253" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="284" t="s">
+      <c r="D11" s="257" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="284" t="s">
+      <c r="E11" s="257" t="s">
         <v>274</v>
       </c>
-      <c r="F11" s="254" t="s">
+      <c r="F11" s="253" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="254" t="s">
+      <c r="G11" s="253" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="254" t="s">
+      <c r="H11" s="253" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="260" t="s">
+      <c r="I11" s="264" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="262" t="s">
+      <c r="J11" s="266" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="262" t="s">
+      <c r="K11" s="266" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="265" t="s">
+      <c r="L11" s="269" t="s">
         <v>42</v>
       </c>
-      <c r="M11" s="262" t="s">
+      <c r="M11" s="266" t="s">
         <v>285</v>
       </c>
-      <c r="N11" s="262" t="s">
+      <c r="N11" s="266" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="255"/>
-      <c r="B12" s="283"/>
-      <c r="C12" s="255"/>
-      <c r="D12" s="285"/>
-      <c r="E12" s="285"/>
-      <c r="F12" s="255"/>
-      <c r="G12" s="255"/>
-      <c r="H12" s="255"/>
-      <c r="I12" s="261"/>
-      <c r="J12" s="263"/>
-      <c r="K12" s="263"/>
-      <c r="L12" s="266"/>
-      <c r="M12" s="263"/>
-      <c r="N12" s="263"/>
-    </row>
-    <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="255"/>
-      <c r="B13" s="283"/>
-      <c r="C13" s="255"/>
-      <c r="D13" s="285"/>
-      <c r="E13" s="285"/>
-      <c r="F13" s="255"/>
-      <c r="G13" s="255"/>
-      <c r="H13" s="255"/>
-      <c r="I13" s="261"/>
-      <c r="J13" s="263"/>
-      <c r="K13" s="264"/>
-      <c r="L13" s="266"/>
+    <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="254"/>
+      <c r="B12" s="256"/>
+      <c r="C12" s="254"/>
+      <c r="D12" s="258"/>
+      <c r="E12" s="258"/>
+      <c r="F12" s="254"/>
+      <c r="G12" s="254"/>
+      <c r="H12" s="254"/>
+      <c r="I12" s="265"/>
+      <c r="J12" s="267"/>
+      <c r="K12" s="267"/>
+      <c r="L12" s="270"/>
+      <c r="M12" s="267"/>
+      <c r="N12" s="267"/>
+    </row>
+    <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="254"/>
+      <c r="B13" s="256"/>
+      <c r="C13" s="254"/>
+      <c r="D13" s="258"/>
+      <c r="E13" s="258"/>
+      <c r="F13" s="254"/>
+      <c r="G13" s="254"/>
+      <c r="H13" s="254"/>
+      <c r="I13" s="265"/>
+      <c r="J13" s="267"/>
+      <c r="K13" s="268"/>
+      <c r="L13" s="270"/>
       <c r="M13" s="140" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 14/11</v>
@@ -6063,7 +6137,7 @@
         <v>VTO 14/11</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>121</v>
       </c>
@@ -6109,12 +6183,12 @@
         <v>120735.58364424</v>
       </c>
       <c r="O14" s="121"/>
-      <c r="Q14" s="253" t="s">
+      <c r="Q14" s="259" t="s">
         <v>259</v>
       </c>
-      <c r="R14" s="253"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R14" s="259"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="35" t="s">
@@ -6156,10 +6230,10 @@
         <v>143094.02505984006</v>
       </c>
       <c r="O15" s="121"/>
-      <c r="Q15" s="253"/>
-      <c r="R15" s="253"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q15" s="259"/>
+      <c r="R15" s="259"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>121</v>
       </c>
@@ -6211,7 +6285,7 @@
         <v>113901.49400400001</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>121</v>
       </c>
@@ -6263,7 +6337,7 @@
         <v>134994.36326400004</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>121</v>
       </c>
@@ -6315,7 +6389,7 @@
         <v>127611.859023</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="57" t="s">
         <v>123</v>
       </c>
@@ -6371,7 +6445,7 @@
         <v>157141.87598700004</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="57" t="s">
         <v>124</v>
       </c>
@@ -6428,7 +6502,7 @@
         <v>183507.96256200003</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="57" t="s">
         <v>123</v>
       </c>
@@ -6478,7 +6552,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="57" t="s">
         <v>125</v>
       </c>
@@ -6532,7 +6606,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="57" t="s">
         <v>125</v>
       </c>
@@ -6581,7 +6655,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="57" t="s">
         <v>125</v>
       </c>
@@ -6633,7 +6707,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="57" t="s">
         <v>123</v>
       </c>
@@ -6684,7 +6758,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="57" t="s">
         <v>124</v>
       </c>
@@ -6734,7 +6808,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="57" t="s">
         <v>123</v>
       </c>
@@ -6781,7 +6855,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="57" t="s">
         <v>125</v>
       </c>
@@ -6830,7 +6904,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="57" t="s">
         <v>125</v>
       </c>
@@ -6879,7 +6953,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="57" t="s">
         <v>125</v>
       </c>
@@ -6926,7 +7000,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="57" t="s">
         <v>123</v>
       </c>
@@ -6976,7 +7050,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="57" t="s">
         <v>124</v>
       </c>
@@ -7028,7 +7102,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A33" s="57" t="s">
         <v>123</v>
       </c>
@@ -7078,7 +7152,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A34" s="149" t="s">
         <v>125</v>
       </c>
@@ -7128,7 +7202,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="35" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A35" s="57" t="s">
         <v>125</v>
       </c>
@@ -7179,7 +7253,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="36" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A36" s="57" t="s">
         <v>125</v>
       </c>
@@ -7226,7 +7300,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A37" s="57" t="s">
         <v>123</v>
       </c>
@@ -7279,7 +7353,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A38" s="57" t="s">
         <v>124</v>
       </c>
@@ -7329,7 +7403,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="149" t="s">
         <v>123</v>
       </c>
@@ -7477,7 +7551,7 @@
       <c r="DH39" s="74"/>
       <c r="DI39" s="74"/>
     </row>
-    <row r="40" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="149" t="s">
         <v>125</v>
       </c>
@@ -7622,7 +7696,7 @@
       <c r="DH40" s="74"/>
       <c r="DI40" s="74"/>
     </row>
-    <row r="41" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="149" t="s">
         <v>125</v>
       </c>
@@ -7772,7 +7846,7 @@
       <c r="DH41" s="74"/>
       <c r="DI41" s="74"/>
     </row>
-    <row r="42" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="149" t="s">
         <v>125</v>
       </c>
@@ -7917,7 +7991,7 @@
       <c r="DH42" s="74"/>
       <c r="DI42" s="74"/>
     </row>
-    <row r="43" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A43" s="57" t="s">
         <v>123</v>
       </c>
@@ -7967,7 +8041,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A44" s="57" t="s">
         <v>124</v>
       </c>
@@ -8019,7 +8093,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A45" s="57" t="s">
         <v>123</v>
       </c>
@@ -8075,7 +8149,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="46" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A46" s="57" t="s">
         <v>125</v>
       </c>
@@ -8128,7 +8202,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="47" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A47" s="57" t="s">
         <v>125</v>
       </c>
@@ -8180,7 +8254,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="48" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A48" s="57" t="s">
         <v>125</v>
       </c>
@@ -8230,7 +8304,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="57" t="s">
         <v>123</v>
       </c>
@@ -8280,7 +8354,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="57" t="s">
         <v>124</v>
       </c>
@@ -8331,7 +8405,7 @@
       </c>
       <c r="P50" s="43"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="57" t="s">
         <v>123</v>
       </c>
@@ -8382,7 +8456,7 @@
       </c>
       <c r="P51" s="43"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="57" t="s">
         <v>125</v>
       </c>
@@ -8435,7 +8509,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="57" t="s">
         <v>125</v>
       </c>
@@ -8484,7 +8558,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="57" t="s">
         <v>125</v>
       </c>
@@ -8534,7 +8608,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="57" t="s">
         <v>123</v>
       </c>
@@ -8585,7 +8659,7 @@
       </c>
       <c r="Q55" s="59"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="57" t="s">
         <v>124</v>
       </c>
@@ -8637,7 +8711,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="57" t="s">
         <v>123</v>
       </c>
@@ -8687,7 +8761,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="57" t="s">
         <v>125</v>
       </c>
@@ -8737,7 +8811,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="57" t="s">
         <v>125</v>
       </c>
@@ -8790,7 +8864,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="57" t="s">
         <v>125</v>
       </c>
@@ -8843,7 +8917,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="57" t="s">
         <v>123</v>
       </c>
@@ -8893,7 +8967,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="57" t="s">
         <v>124</v>
       </c>
@@ -8943,7 +9017,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="57" t="s">
         <v>123</v>
       </c>
@@ -8993,7 +9067,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="57" t="s">
         <v>125</v>
       </c>
@@ -9045,7 +9119,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="57" t="s">
         <v>125</v>
       </c>
@@ -9092,7 +9166,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="57" t="s">
         <v>125</v>
       </c>
@@ -9142,7 +9216,7 @@
         <v>0.48000000000000026</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="57" t="s">
         <v>123</v>
       </c>
@@ -9192,7 +9266,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="149" t="s">
         <v>124</v>
       </c>
@@ -9239,7 +9313,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="57" t="s">
         <v>123</v>
       </c>
@@ -9289,7 +9363,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="57" t="s">
         <v>125</v>
       </c>
@@ -9338,7 +9412,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="57" t="s">
         <v>125</v>
       </c>
@@ -9391,7 +9465,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="57" t="s">
         <v>125</v>
       </c>
@@ -9441,7 +9515,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="57" t="s">
         <v>126</v>
       </c>
@@ -9491,7 +9565,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="57" t="s">
         <v>123</v>
       </c>
@@ -9541,7 +9615,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="57" t="s">
         <v>125</v>
       </c>
@@ -9591,7 +9665,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="57" t="s">
         <v>125</v>
       </c>
@@ -9643,7 +9717,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="57" t="s">
         <v>125</v>
       </c>
@@ -9692,7 +9766,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="57" t="s">
         <v>126</v>
       </c>
@@ -9742,7 +9816,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="57" t="s">
         <v>123</v>
       </c>
@@ -9791,7 +9865,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="57" t="s">
         <v>125</v>
       </c>
@@ -9838,7 +9912,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="57" t="s">
         <v>125</v>
       </c>
@@ -9890,7 +9964,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="57" t="s">
         <v>125</v>
       </c>
@@ -9943,7 +10017,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="57" t="s">
         <v>126</v>
       </c>
@@ -9993,7 +10067,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="57" t="s">
         <v>123</v>
       </c>
@@ -10043,7 +10117,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="57" t="s">
         <v>125</v>
       </c>
@@ -10093,7 +10167,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="57" t="s">
         <v>125</v>
       </c>
@@ -10143,7 +10217,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="114" t="s">
         <v>125</v>
       </c>
@@ -10191,7 +10265,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="114"/>
       <c r="B88" s="35"/>
       <c r="C88" s="35" t="s">
@@ -10239,7 +10313,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="114"/>
       <c r="B89" s="35"/>
       <c r="C89" s="35" t="s">
@@ -10287,7 +10361,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="114"/>
       <c r="B90" s="35"/>
       <c r="C90" s="35" t="s">
@@ -10335,7 +10409,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="114"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35" t="s">
@@ -10383,7 +10457,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="114"/>
       <c r="B92" s="35"/>
       <c r="C92" s="222" t="s">
@@ -10434,7 +10508,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="114"/>
       <c r="B93" s="35"/>
       <c r="C93" s="35" t="s">
@@ -10482,7 +10556,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" s="114"/>
       <c r="B94" s="35"/>
       <c r="C94" s="35" t="s">
@@ -10530,7 +10604,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="114"/>
       <c r="B95" s="35"/>
       <c r="C95" s="35" t="s">
@@ -10578,7 +10652,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" s="114"/>
       <c r="B96" s="35"/>
       <c r="C96" s="35" t="s">
@@ -10625,7 +10699,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="114"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35" t="s">
@@ -10670,7 +10744,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="114"/>
       <c r="B98" s="35"/>
       <c r="C98" s="35" t="s">
@@ -10718,7 +10792,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="114"/>
       <c r="B99" s="35"/>
       <c r="C99" s="35" t="s">
@@ -10766,7 +10840,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="114"/>
       <c r="B100" s="35"/>
       <c r="C100" s="35" t="s">
@@ -10814,7 +10888,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="114"/>
       <c r="B101" s="35"/>
       <c r="C101" s="35" t="s">
@@ -10862,7 +10936,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="114"/>
       <c r="B102" s="35"/>
       <c r="C102" s="35" t="s">
@@ -10910,7 +10984,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="114"/>
       <c r="B103" s="35"/>
       <c r="C103" s="206" t="s">
@@ -10958,7 +11032,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="114"/>
       <c r="B104" s="35"/>
       <c r="C104" s="35" t="s">
@@ -11006,7 +11080,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="114"/>
       <c r="B105" s="35"/>
       <c r="C105" s="35" t="s">
@@ -11054,7 +11128,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="114"/>
       <c r="B106" s="35"/>
       <c r="C106" s="35" t="s">
@@ -11101,7 +11175,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="114"/>
       <c r="B107" s="35"/>
       <c r="C107" s="35" t="s">
@@ -11149,7 +11223,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="114"/>
       <c r="B108" s="35"/>
       <c r="C108" s="35" t="s">
@@ -11197,7 +11271,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="114"/>
       <c r="B109" s="35"/>
       <c r="C109" s="35" t="s">
@@ -11245,7 +11319,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="114"/>
       <c r="B110" s="35"/>
       <c r="C110" s="35" t="s">
@@ -11293,7 +11367,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="114"/>
       <c r="B111" s="35"/>
       <c r="C111" s="206" t="s">
@@ -11341,7 +11415,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="114"/>
       <c r="B112" s="35"/>
       <c r="C112" s="35" t="s">
@@ -11389,7 +11463,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="114"/>
       <c r="B113" s="35"/>
       <c r="C113" s="35" t="s">
@@ -11437,7 +11511,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="114"/>
       <c r="B114" s="35"/>
       <c r="C114" s="35" t="s">
@@ -11485,7 +11559,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="114"/>
       <c r="B115" s="35"/>
       <c r="C115" s="35" t="s">
@@ -11533,7 +11607,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="114"/>
       <c r="B116" s="35"/>
       <c r="C116" s="35" t="s">
@@ -11580,7 +11654,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" s="114"/>
       <c r="B117" s="35"/>
       <c r="C117" s="35" t="s">
@@ -11625,7 +11699,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="114"/>
       <c r="B118" s="35"/>
       <c r="C118" s="35" t="s">
@@ -11676,7 +11750,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="135"/>
       <c r="B119" s="35"/>
       <c r="C119" s="35" t="s">
@@ -11724,7 +11798,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="135"/>
       <c r="B120" s="35"/>
       <c r="C120" s="35" t="s">
@@ -11772,7 +11846,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" s="135"/>
       <c r="B121" s="35"/>
       <c r="C121" s="196" t="s">
@@ -11819,7 +11893,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" s="135"/>
       <c r="B122" s="35"/>
       <c r="C122" s="35" t="s">
@@ -11867,7 +11941,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" s="135"/>
       <c r="B123" s="35"/>
       <c r="C123" s="35" t="s">
@@ -11915,7 +11989,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="135"/>
       <c r="B124" s="35"/>
       <c r="C124" s="35" t="s">
@@ -11960,7 +12034,7 @@
         <v>1.0600000000000007</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" s="135"/>
       <c r="B125" s="35"/>
       <c r="C125" s="35" t="s">
@@ -12005,7 +12079,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" s="135"/>
       <c r="B126" s="35"/>
       <c r="C126" s="206" t="s">
@@ -12053,7 +12127,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127" s="135"/>
       <c r="B127" s="35"/>
       <c r="C127" s="35" t="s">
@@ -12101,7 +12175,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128" s="135"/>
       <c r="B128" s="35"/>
       <c r="C128" s="35" t="s">
@@ -12149,7 +12223,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A129" s="135"/>
       <c r="B129" s="35"/>
       <c r="C129" s="35" t="s">
@@ -12197,7 +12271,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" s="135" t="s">
         <v>26</v>
       </c>
@@ -12247,7 +12321,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" s="135" t="s">
         <v>26</v>
       </c>
@@ -12297,7 +12371,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" s="53" t="s">
         <v>26</v>
       </c>
@@ -12315,7 +12389,7 @@
       <c r="M132" s="5"/>
       <c r="N132" s="8"/>
     </row>
-    <row r="133" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="27"/>
       <c r="B133" s="27"/>
       <c r="C133" s="27"/>
@@ -12356,41 +12430,41 @@
       </c>
       <c r="P133" s="59"/>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K134" s="61">
         <f>K133-L1</f>
         <v>1338773.6948400009</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="257"/>
-      <c r="D135" s="257"/>
-      <c r="E135" s="257"/>
-      <c r="F135" s="257"/>
-      <c r="G135" s="257"/>
-      <c r="H135" s="257"/>
-      <c r="I135" s="257"/>
-      <c r="J135" s="257"/>
-      <c r="K135" s="257"/>
-      <c r="L135" s="257"/>
-      <c r="M135" s="257"/>
-      <c r="N135" s="257"/>
-    </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="257"/>
-      <c r="D136" s="257"/>
-      <c r="E136" s="257"/>
-      <c r="F136" s="257"/>
-      <c r="G136" s="257"/>
-      <c r="H136" s="257"/>
-      <c r="I136" s="257"/>
-      <c r="J136" s="257"/>
-      <c r="K136" s="257"/>
-      <c r="L136" s="257"/>
-      <c r="M136" s="257"/>
-      <c r="N136" s="257"/>
-    </row>
-    <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C135" s="261"/>
+      <c r="D135" s="261"/>
+      <c r="E135" s="261"/>
+      <c r="F135" s="261"/>
+      <c r="G135" s="261"/>
+      <c r="H135" s="261"/>
+      <c r="I135" s="261"/>
+      <c r="J135" s="261"/>
+      <c r="K135" s="261"/>
+      <c r="L135" s="261"/>
+      <c r="M135" s="261"/>
+      <c r="N135" s="261"/>
+    </row>
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C136" s="261"/>
+      <c r="D136" s="261"/>
+      <c r="E136" s="261"/>
+      <c r="F136" s="261"/>
+      <c r="G136" s="261"/>
+      <c r="H136" s="261"/>
+      <c r="I136" s="261"/>
+      <c r="J136" s="261"/>
+      <c r="K136" s="261"/>
+      <c r="L136" s="261"/>
+      <c r="M136" s="261"/>
+      <c r="N136" s="261"/>
+    </row>
+    <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="79"/>
       <c r="D137" s="79"/>
       <c r="E137" s="79"/>
@@ -12404,121 +12478,121 @@
       <c r="M137" s="79"/>
       <c r="N137" s="79"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C138" s="257" t="s">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C138" s="261" t="s">
         <v>265</v>
       </c>
-      <c r="D138" s="257"/>
-      <c r="E138" s="257"/>
-      <c r="F138" s="257"/>
-      <c r="G138" s="257"/>
-      <c r="H138" s="257"/>
-      <c r="I138" s="257"/>
-      <c r="J138" s="257"/>
-      <c r="K138" s="257"/>
-      <c r="L138" s="257"/>
-      <c r="M138" s="257"/>
-      <c r="N138" s="257"/>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C139" s="257"/>
-      <c r="D139" s="257"/>
-      <c r="E139" s="257"/>
-      <c r="F139" s="257"/>
-      <c r="G139" s="257"/>
-      <c r="H139" s="257"/>
-      <c r="I139" s="257"/>
-      <c r="J139" s="257"/>
-      <c r="K139" s="257"/>
-      <c r="L139" s="257"/>
-      <c r="M139" s="257"/>
-      <c r="N139" s="257"/>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C140" s="257"/>
-      <c r="D140" s="257"/>
-      <c r="E140" s="257"/>
-      <c r="F140" s="257"/>
-      <c r="G140" s="257"/>
-      <c r="H140" s="257"/>
-      <c r="I140" s="257"/>
-      <c r="J140" s="257"/>
-      <c r="K140" s="257"/>
-      <c r="L140" s="257"/>
-      <c r="M140" s="257"/>
-      <c r="N140" s="257"/>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C141" s="257"/>
-      <c r="D141" s="257"/>
-      <c r="E141" s="257"/>
-      <c r="F141" s="257"/>
-      <c r="G141" s="257"/>
-      <c r="H141" s="257"/>
-      <c r="I141" s="257"/>
-      <c r="J141" s="257"/>
-      <c r="K141" s="257"/>
-      <c r="L141" s="257"/>
-      <c r="M141" s="257"/>
-      <c r="N141" s="257"/>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C142" s="257"/>
-      <c r="D142" s="257"/>
-      <c r="E142" s="257"/>
-      <c r="F142" s="257"/>
-      <c r="G142" s="257"/>
-      <c r="H142" s="257"/>
-      <c r="I142" s="257"/>
-      <c r="J142" s="257"/>
-      <c r="K142" s="257"/>
-      <c r="L142" s="257"/>
-      <c r="M142" s="257"/>
-      <c r="N142" s="257"/>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C143" s="257"/>
-      <c r="D143" s="257"/>
-      <c r="E143" s="257"/>
-      <c r="F143" s="257"/>
-      <c r="G143" s="257"/>
-      <c r="H143" s="257"/>
-      <c r="I143" s="257"/>
-      <c r="J143" s="257"/>
-      <c r="K143" s="257"/>
-      <c r="L143" s="257"/>
-      <c r="M143" s="257"/>
-      <c r="N143" s="257"/>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C144" s="257"/>
-      <c r="D144" s="257"/>
-      <c r="E144" s="257"/>
-      <c r="F144" s="257"/>
-      <c r="G144" s="257"/>
-      <c r="H144" s="257"/>
-      <c r="I144" s="257"/>
-      <c r="J144" s="257"/>
-      <c r="K144" s="257"/>
-      <c r="L144" s="257"/>
-      <c r="M144" s="257"/>
-      <c r="N144" s="257"/>
-    </row>
-    <row r="145" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C145" s="257"/>
-      <c r="D145" s="257"/>
-      <c r="E145" s="257"/>
-      <c r="F145" s="257"/>
-      <c r="G145" s="257"/>
-      <c r="H145" s="257"/>
-      <c r="I145" s="257"/>
-      <c r="J145" s="257"/>
-      <c r="K145" s="257"/>
-      <c r="L145" s="257"/>
-      <c r="M145" s="257"/>
-      <c r="N145" s="257"/>
-    </row>
-    <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D138" s="261"/>
+      <c r="E138" s="261"/>
+      <c r="F138" s="261"/>
+      <c r="G138" s="261"/>
+      <c r="H138" s="261"/>
+      <c r="I138" s="261"/>
+      <c r="J138" s="261"/>
+      <c r="K138" s="261"/>
+      <c r="L138" s="261"/>
+      <c r="M138" s="261"/>
+      <c r="N138" s="261"/>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C139" s="261"/>
+      <c r="D139" s="261"/>
+      <c r="E139" s="261"/>
+      <c r="F139" s="261"/>
+      <c r="G139" s="261"/>
+      <c r="H139" s="261"/>
+      <c r="I139" s="261"/>
+      <c r="J139" s="261"/>
+      <c r="K139" s="261"/>
+      <c r="L139" s="261"/>
+      <c r="M139" s="261"/>
+      <c r="N139" s="261"/>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C140" s="261"/>
+      <c r="D140" s="261"/>
+      <c r="E140" s="261"/>
+      <c r="F140" s="261"/>
+      <c r="G140" s="261"/>
+      <c r="H140" s="261"/>
+      <c r="I140" s="261"/>
+      <c r="J140" s="261"/>
+      <c r="K140" s="261"/>
+      <c r="L140" s="261"/>
+      <c r="M140" s="261"/>
+      <c r="N140" s="261"/>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C141" s="261"/>
+      <c r="D141" s="261"/>
+      <c r="E141" s="261"/>
+      <c r="F141" s="261"/>
+      <c r="G141" s="261"/>
+      <c r="H141" s="261"/>
+      <c r="I141" s="261"/>
+      <c r="J141" s="261"/>
+      <c r="K141" s="261"/>
+      <c r="L141" s="261"/>
+      <c r="M141" s="261"/>
+      <c r="N141" s="261"/>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C142" s="261"/>
+      <c r="D142" s="261"/>
+      <c r="E142" s="261"/>
+      <c r="F142" s="261"/>
+      <c r="G142" s="261"/>
+      <c r="H142" s="261"/>
+      <c r="I142" s="261"/>
+      <c r="J142" s="261"/>
+      <c r="K142" s="261"/>
+      <c r="L142" s="261"/>
+      <c r="M142" s="261"/>
+      <c r="N142" s="261"/>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C143" s="261"/>
+      <c r="D143" s="261"/>
+      <c r="E143" s="261"/>
+      <c r="F143" s="261"/>
+      <c r="G143" s="261"/>
+      <c r="H143" s="261"/>
+      <c r="I143" s="261"/>
+      <c r="J143" s="261"/>
+      <c r="K143" s="261"/>
+      <c r="L143" s="261"/>
+      <c r="M143" s="261"/>
+      <c r="N143" s="261"/>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C144" s="261"/>
+      <c r="D144" s="261"/>
+      <c r="E144" s="261"/>
+      <c r="F144" s="261"/>
+      <c r="G144" s="261"/>
+      <c r="H144" s="261"/>
+      <c r="I144" s="261"/>
+      <c r="J144" s="261"/>
+      <c r="K144" s="261"/>
+      <c r="L144" s="261"/>
+      <c r="M144" s="261"/>
+      <c r="N144" s="261"/>
+    </row>
+    <row r="145" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C145" s="261"/>
+      <c r="D145" s="261"/>
+      <c r="E145" s="261"/>
+      <c r="F145" s="261"/>
+      <c r="G145" s="261"/>
+      <c r="H145" s="261"/>
+      <c r="I145" s="261"/>
+      <c r="J145" s="261"/>
+      <c r="K145" s="261"/>
+      <c r="L145" s="261"/>
+      <c r="M145" s="261"/>
+      <c r="N145" s="261"/>
+    </row>
+    <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="79"/>
       <c r="D146" s="79"/>
       <c r="E146" s="79"/>
@@ -12532,7 +12606,7 @@
       <c r="M146" s="79"/>
       <c r="N146" s="79"/>
     </row>
-    <row r="147" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="79"/>
       <c r="D147" s="79"/>
       <c r="E147" s="79"/>
@@ -12546,118 +12620,112 @@
       <c r="M147" s="79"/>
       <c r="N147" s="79"/>
     </row>
-    <row r="148" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C148" s="256" t="s">
+    <row r="148" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C148" s="260" t="s">
         <v>264</v>
       </c>
-      <c r="D148" s="256"/>
-      <c r="E148" s="256"/>
-      <c r="F148" s="256"/>
-      <c r="G148" s="256"/>
-      <c r="H148" s="256"/>
-      <c r="I148" s="256"/>
-      <c r="J148" s="256"/>
-      <c r="K148" s="256"/>
-      <c r="L148" s="256"/>
-      <c r="M148" s="256"/>
-      <c r="N148" s="256"/>
-    </row>
-    <row r="149" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C149" s="256"/>
-      <c r="D149" s="256"/>
-      <c r="E149" s="256"/>
-      <c r="F149" s="256"/>
-      <c r="G149" s="256"/>
-      <c r="H149" s="256"/>
-      <c r="I149" s="256"/>
-      <c r="J149" s="256"/>
-      <c r="K149" s="256"/>
-      <c r="L149" s="256"/>
-      <c r="M149" s="256"/>
-      <c r="N149" s="256"/>
-    </row>
-    <row r="150" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C150" s="256"/>
-      <c r="D150" s="256"/>
-      <c r="E150" s="256"/>
-      <c r="F150" s="256"/>
-      <c r="G150" s="256"/>
-      <c r="H150" s="256"/>
-      <c r="I150" s="256"/>
-      <c r="J150" s="256"/>
-      <c r="K150" s="256"/>
-      <c r="L150" s="256"/>
-      <c r="M150" s="256"/>
-      <c r="N150" s="256"/>
+      <c r="D148" s="260"/>
+      <c r="E148" s="260"/>
+      <c r="F148" s="260"/>
+      <c r="G148" s="260"/>
+      <c r="H148" s="260"/>
+      <c r="I148" s="260"/>
+      <c r="J148" s="260"/>
+      <c r="K148" s="260"/>
+      <c r="L148" s="260"/>
+      <c r="M148" s="260"/>
+      <c r="N148" s="260"/>
+    </row>
+    <row r="149" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C149" s="260"/>
+      <c r="D149" s="260"/>
+      <c r="E149" s="260"/>
+      <c r="F149" s="260"/>
+      <c r="G149" s="260"/>
+      <c r="H149" s="260"/>
+      <c r="I149" s="260"/>
+      <c r="J149" s="260"/>
+      <c r="K149" s="260"/>
+      <c r="L149" s="260"/>
+      <c r="M149" s="260"/>
+      <c r="N149" s="260"/>
+    </row>
+    <row r="150" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C150" s="260"/>
+      <c r="D150" s="260"/>
+      <c r="E150" s="260"/>
+      <c r="F150" s="260"/>
+      <c r="G150" s="260"/>
+      <c r="H150" s="260"/>
+      <c r="I150" s="260"/>
+      <c r="J150" s="260"/>
+      <c r="K150" s="260"/>
+      <c r="L150" s="260"/>
+      <c r="M150" s="260"/>
+      <c r="N150" s="260"/>
       <c r="P150" s="86">
         <f>L1-K133</f>
         <v>-1338773.6948400009</v>
       </c>
     </row>
-    <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="256"/>
-      <c r="D151" s="256"/>
-      <c r="E151" s="256"/>
-      <c r="F151" s="256"/>
-      <c r="G151" s="256"/>
-      <c r="H151" s="256"/>
-      <c r="I151" s="256"/>
-      <c r="J151" s="256"/>
-      <c r="K151" s="256"/>
-      <c r="L151" s="256"/>
-      <c r="M151" s="256"/>
-      <c r="N151" s="256"/>
-    </row>
-    <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="256"/>
-      <c r="D152" s="256"/>
-      <c r="E152" s="256"/>
-      <c r="F152" s="256"/>
-      <c r="G152" s="256"/>
-      <c r="H152" s="256"/>
-      <c r="I152" s="256"/>
-      <c r="J152" s="256"/>
-      <c r="K152" s="256"/>
-      <c r="L152" s="256"/>
-      <c r="M152" s="256"/>
-      <c r="N152" s="256"/>
-    </row>
-    <row r="153" spans="3:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="256"/>
-      <c r="D153" s="256"/>
-      <c r="E153" s="256"/>
-      <c r="F153" s="256"/>
-      <c r="G153" s="256"/>
-      <c r="H153" s="256"/>
-      <c r="I153" s="256"/>
-      <c r="J153" s="256"/>
-      <c r="K153" s="256"/>
-      <c r="L153" s="256"/>
-      <c r="M153" s="256"/>
-      <c r="N153" s="256"/>
-    </row>
-    <row r="154" spans="3:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="256"/>
-      <c r="D154" s="256"/>
-      <c r="E154" s="256"/>
-      <c r="F154" s="256"/>
-      <c r="G154" s="256"/>
-      <c r="H154" s="256"/>
-      <c r="I154" s="256"/>
-      <c r="J154" s="256"/>
-      <c r="K154" s="256"/>
-      <c r="L154" s="256"/>
-      <c r="M154" s="256"/>
-      <c r="N154" s="256"/>
+    <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C151" s="260"/>
+      <c r="D151" s="260"/>
+      <c r="E151" s="260"/>
+      <c r="F151" s="260"/>
+      <c r="G151" s="260"/>
+      <c r="H151" s="260"/>
+      <c r="I151" s="260"/>
+      <c r="J151" s="260"/>
+      <c r="K151" s="260"/>
+      <c r="L151" s="260"/>
+      <c r="M151" s="260"/>
+      <c r="N151" s="260"/>
+    </row>
+    <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C152" s="260"/>
+      <c r="D152" s="260"/>
+      <c r="E152" s="260"/>
+      <c r="F152" s="260"/>
+      <c r="G152" s="260"/>
+      <c r="H152" s="260"/>
+      <c r="I152" s="260"/>
+      <c r="J152" s="260"/>
+      <c r="K152" s="260"/>
+      <c r="L152" s="260"/>
+      <c r="M152" s="260"/>
+      <c r="N152" s="260"/>
+    </row>
+    <row r="153" spans="3:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C153" s="260"/>
+      <c r="D153" s="260"/>
+      <c r="E153" s="260"/>
+      <c r="F153" s="260"/>
+      <c r="G153" s="260"/>
+      <c r="H153" s="260"/>
+      <c r="I153" s="260"/>
+      <c r="J153" s="260"/>
+      <c r="K153" s="260"/>
+      <c r="L153" s="260"/>
+      <c r="M153" s="260"/>
+      <c r="N153" s="260"/>
+    </row>
+    <row r="154" spans="3:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C154" s="260"/>
+      <c r="D154" s="260"/>
+      <c r="E154" s="260"/>
+      <c r="F154" s="260"/>
+      <c r="G154" s="260"/>
+      <c r="H154" s="260"/>
+      <c r="I154" s="260"/>
+      <c r="J154" s="260"/>
+      <c r="K154" s="260"/>
+      <c r="L154" s="260"/>
+      <c r="M154" s="260"/>
+      <c r="N154" s="260"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
     <mergeCell ref="Q14:R15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:N154"/>
@@ -12673,6 +12741,12 @@
     <mergeCell ref="N11:N12"/>
     <mergeCell ref="C5:N8"/>
     <mergeCell ref="C9:N10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12684,9 +12758,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
   <dimension ref="B4:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="240" t="s">
         <v>357</v>
       </c>
@@ -12702,20 +12776,331 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0166F049-50A4-4ACA-9F6E-1C2F2AD24458}">
+  <dimension ref="A2:J27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C3" s="287" t="str">
+        <f>RESUMEN!C5</f>
+        <v>PERÍODO: OCTUBRE</v>
+      </c>
+      <c r="D3" s="288"/>
+      <c r="E3" s="288"/>
+      <c r="F3" s="288" t="str">
+        <f>[1]RESUMEN!A22</f>
+        <v xml:space="preserve">Sueldo encargada Sonia Arzamendia Galeano </v>
+      </c>
+      <c r="G3" s="288"/>
+      <c r="H3" s="288"/>
+      <c r="I3" s="288"/>
+      <c r="J3" s="289"/>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="1"/>
+      <c r="J4" s="290"/>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="1" t="str">
+        <f>RESUMEN!A26</f>
+        <v xml:space="preserve">Haberes </v>
+      </c>
+      <c r="G5" s="43">
+        <f>RESUMEN!D26</f>
+        <v>1026046</v>
+      </c>
+      <c r="H5" s="291" t="s">
+        <v>358</v>
+      </c>
+      <c r="I5" s="291"/>
+      <c r="J5" s="292"/>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="1" t="str">
+        <f>RESUMEN!A27</f>
+        <v>Plus pileta</v>
+      </c>
+      <c r="G6" s="43">
+        <f>RESUMEN!D27</f>
+        <v>35809.699999999997</v>
+      </c>
+      <c r="H6" s="291" t="s">
+        <v>359</v>
+      </c>
+      <c r="I6" s="291"/>
+      <c r="J6" s="292"/>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="1" t="str">
+        <f>RESUMEN!A28</f>
+        <v>Plus retiro de basura</v>
+      </c>
+      <c r="G7" s="43">
+        <f>RESUMEN!D28</f>
+        <v>124792</v>
+      </c>
+      <c r="H7" s="291"/>
+      <c r="I7" s="291"/>
+      <c r="J7" s="292"/>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="1" t="str">
+        <f>RESUMEN!A29</f>
+        <v>Plus cochera</v>
+      </c>
+      <c r="G8" s="43">
+        <f>RESUMEN!D29</f>
+        <v>21286.799999999999</v>
+      </c>
+      <c r="J8" s="290"/>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="1" t="str">
+        <f>RESUMEN!A30</f>
+        <v>Adicional Viaticos</v>
+      </c>
+      <c r="G9" s="43">
+        <f>RESUMEN!D30</f>
+        <v>59852.7</v>
+      </c>
+      <c r="H9" s="291" t="s">
+        <v>360</v>
+      </c>
+      <c r="I9" s="291"/>
+      <c r="J9" s="292"/>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="1" t="str">
+        <f>RESUMEN!A31</f>
+        <v>Adicional remuneracion</v>
+      </c>
+      <c r="G10" s="43">
+        <f>RESUMEN!D31</f>
+        <v>50000</v>
+      </c>
+      <c r="H10" s="291" t="s">
+        <v>359</v>
+      </c>
+      <c r="I10" s="291"/>
+      <c r="J10" s="292"/>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="1"/>
+      <c r="H11" s="291"/>
+      <c r="I11" s="291"/>
+      <c r="J11" s="292"/>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="293" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="294">
+        <f>SUM(G5:G11)</f>
+        <v>1317787.2</v>
+      </c>
+      <c r="J12" s="290"/>
+    </row>
+    <row r="13" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="295"/>
+      <c r="D13" s="296"/>
+      <c r="E13" s="296"/>
+      <c r="F13" s="296"/>
+      <c r="G13" s="296"/>
+      <c r="H13" s="296"/>
+      <c r="I13" s="296"/>
+      <c r="J13" s="297"/>
+    </row>
+    <row r="15" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="287" t="str">
+        <f>C3</f>
+        <v>PERÍODO: OCTUBRE</v>
+      </c>
+      <c r="D16" s="288"/>
+      <c r="E16" s="288"/>
+      <c r="F16" s="288" t="str">
+        <f>[1]RESUMEN!A30</f>
+        <v>Sueldo encargada Miriam</v>
+      </c>
+      <c r="G16" s="288"/>
+      <c r="H16" s="288"/>
+      <c r="I16" s="288"/>
+      <c r="J16" s="289"/>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="1"/>
+      <c r="J17" s="290"/>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="1"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="291" t="s">
+        <v>358</v>
+      </c>
+      <c r="I18" s="291"/>
+      <c r="J18" s="292"/>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="1" t="str">
+        <f>RESUMEN!A34</f>
+        <v xml:space="preserve">Haberes </v>
+      </c>
+      <c r="G19" s="43">
+        <f>RESUMEN!D34</f>
+        <v>513023</v>
+      </c>
+      <c r="H19" s="291" t="s">
+        <v>359</v>
+      </c>
+      <c r="I19" s="291"/>
+      <c r="J19" s="292"/>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="1" t="str">
+        <f>RESUMEN!A35</f>
+        <v>Horas extras</v>
+      </c>
+      <c r="G20" s="43">
+        <f>RESUMEN!D35</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="291"/>
+      <c r="I20" s="291"/>
+      <c r="J20" s="292"/>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="1" t="str">
+        <f>RESUMEN!A36</f>
+        <v>Plus pileta</v>
+      </c>
+      <c r="G21" s="43">
+        <f>RESUMEN!D36</f>
+        <v>35809.699999999997</v>
+      </c>
+      <c r="J21" s="290"/>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="1" t="str">
+        <f>RESUMEN!A37</f>
+        <v>Plus retiro de basura</v>
+      </c>
+      <c r="G22" s="43">
+        <f>RESUMEN!D37</f>
+        <v>124792</v>
+      </c>
+      <c r="H22" s="291" t="s">
+        <v>360</v>
+      </c>
+      <c r="I22" s="291"/>
+      <c r="J22" s="292"/>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="1" t="str">
+        <f>RESUMEN!A38</f>
+        <v>Plus cochera</v>
+      </c>
+      <c r="G23" s="43">
+        <f>RESUMEN!D38</f>
+        <v>21286.799999999999</v>
+      </c>
+      <c r="H23" s="291" t="s">
+        <v>359</v>
+      </c>
+      <c r="I23" s="291"/>
+      <c r="J23" s="292"/>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="1" t="str">
+        <f>RESUMEN!A39</f>
+        <v>Adicional Viaticos</v>
+      </c>
+      <c r="G24" s="43">
+        <f>RESUMEN!D39</f>
+        <v>59852.7</v>
+      </c>
+      <c r="H24" s="291"/>
+      <c r="I24" s="291"/>
+      <c r="J24" s="292"/>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="1" t="str">
+        <f>RESUMEN!A40</f>
+        <v>Adicional remuneracion</v>
+      </c>
+      <c r="G25" s="43">
+        <f>RESUMEN!D40</f>
+        <v>50000</v>
+      </c>
+      <c r="H25" s="298"/>
+      <c r="I25" s="298"/>
+      <c r="J25" s="299"/>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="293" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="294">
+        <f>SUM(G18:G25)</f>
+        <v>804764.2</v>
+      </c>
+      <c r="J26" s="290"/>
+    </row>
+    <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C27" s="295"/>
+      <c r="D27" s="296"/>
+      <c r="E27" s="296"/>
+      <c r="F27" s="296"/>
+      <c r="G27" s="296"/>
+      <c r="H27" s="296"/>
+      <c r="I27" s="296"/>
+      <c r="J27" s="297"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J20"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H23:J24"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H6:J7"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="H10:J11"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A8B3D07-243A-48F3-942B-AB44D486DEC8}">
   <dimension ref="C4:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C4" s="286" t="s">
         <v>287</v>
       </c>
       <c r="D4" s="286"/>
     </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C5" s="145">
         <v>52141.08</v>
       </c>
@@ -12723,7 +13108,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C6" s="145">
         <v>67140.100000000006</v>
       </c>
@@ -12731,7 +13116,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C7" s="145">
         <v>52121.11</v>
       </c>
@@ -12739,7 +13124,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C8" s="145">
         <v>67885.119999999995</v>
       </c>
@@ -12747,7 +13132,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C9" s="145">
         <v>67140.160000000003</v>
       </c>
@@ -12755,7 +13140,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C10" s="145">
         <v>62141.17</v>
       </c>
@@ -12763,7 +13148,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C11" s="145">
         <v>67855.179999999993</v>
       </c>
@@ -12771,7 +13156,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C12" s="145">
         <v>62141.23</v>
       </c>
@@ -12779,7 +13164,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C13" s="145">
         <v>67855.240000000005</v>
       </c>
@@ -12787,7 +13172,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C14" s="145">
         <f>SUM(C5:C13)</f>
         <v>566420.39</v>

--- a/EL MIRADOR/Octubre/Octubre - EL MIRADOR  (1).xlsx
+++ b/EL MIRADOR/Octubre/Octubre - EL MIRADOR  (1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\EL MIRADOR\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\EL MIRADOR\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FA6DB7-6E57-4435-AB19-4FFAEF69F1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BEEFC7-84B5-4E62-946A-5A024F3E311D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="362">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1124,6 +1124,9 @@
   </si>
   <si>
     <t>Aclaracion</t>
+  </si>
+  <si>
+    <t>Transf 10/11</t>
   </si>
 </sst>
 </file>
@@ -2019,6 +2022,18 @@
     <xf numFmtId="4" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2055,26 +2070,14 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2154,8 +2157,17 @@
     <xf numFmtId="1" fontId="19" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2166,22 +2178,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2641,24 +2644,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R169"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.6640625" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
-    <col min="11" max="11" width="15.88671875" customWidth="1"/>
-    <col min="12" max="12" width="16.109375" customWidth="1"/>
+    <col min="6" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.33203125" customWidth="1"/>
+    <col min="17" max="17" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="118"/>
       <c r="B1" s="127"/>
       <c r="C1" s="137" t="s">
@@ -2672,7 +2675,7 @@
       <c r="I1" s="116"/>
       <c r="J1" s="117"/>
     </row>
-    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="119"/>
       <c r="B2" s="128"/>
       <c r="C2" s="128" t="s">
@@ -2686,7 +2689,7 @@
       <c r="I2" s="129"/>
       <c r="J2" s="115"/>
     </row>
-    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="119"/>
       <c r="B3" s="128"/>
       <c r="C3" s="128" t="s">
@@ -2702,7 +2705,7 @@
       <c r="I3" s="129"/>
       <c r="J3" s="115"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="119"/>
       <c r="B4" s="128"/>
       <c r="C4" s="128" t="s">
@@ -2716,7 +2719,7 @@
       <c r="I4" s="129"/>
       <c r="J4" s="115"/>
     </row>
-    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="123"/>
       <c r="B5" s="128"/>
       <c r="C5" s="128" t="s">
@@ -2732,7 +2735,7 @@
       <c r="I5" s="128"/>
       <c r="J5" s="124"/>
     </row>
-    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="123"/>
       <c r="B6" s="128"/>
       <c r="C6" s="128" t="s">
@@ -2746,7 +2749,7 @@
       <c r="I6" s="128"/>
       <c r="J6" s="124"/>
     </row>
-    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="125"/>
       <c r="B7" s="126"/>
       <c r="C7" s="126"/>
@@ -2758,118 +2761,118 @@
       <c r="I7" s="126"/>
       <c r="J7" s="130"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="241" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="249" t="s">
         <v>265</v>
       </c>
-      <c r="B14" s="241"/>
-      <c r="C14" s="241"/>
-      <c r="D14" s="241"/>
-      <c r="E14" s="241"/>
-      <c r="F14" s="241"/>
-      <c r="G14" s="241"/>
-      <c r="H14" s="241"/>
-      <c r="I14" s="241"/>
-      <c r="J14" s="241"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="241"/>
-      <c r="B15" s="241"/>
-      <c r="C15" s="241"/>
-      <c r="D15" s="241"/>
-      <c r="E15" s="241"/>
-      <c r="F15" s="241"/>
-      <c r="G15" s="241"/>
-      <c r="H15" s="241"/>
-      <c r="I15" s="241"/>
-      <c r="J15" s="241"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="241"/>
-      <c r="B16" s="241"/>
-      <c r="C16" s="241"/>
-      <c r="D16" s="241"/>
-      <c r="E16" s="241"/>
-      <c r="F16" s="241"/>
-      <c r="G16" s="241"/>
-      <c r="H16" s="241"/>
-      <c r="I16" s="241"/>
-      <c r="J16" s="241"/>
-    </row>
-    <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="241"/>
-      <c r="B17" s="241"/>
-      <c r="C17" s="241"/>
-      <c r="D17" s="241"/>
-      <c r="E17" s="241"/>
-      <c r="F17" s="241"/>
-      <c r="G17" s="241"/>
-      <c r="H17" s="241"/>
-      <c r="I17" s="241"/>
-      <c r="J17" s="241"/>
-    </row>
-    <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="241"/>
-      <c r="B18" s="241"/>
-      <c r="C18" s="241"/>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="241"/>
-      <c r="G18" s="241"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="241"/>
-      <c r="J18" s="241"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="249"/>
+      <c r="C14" s="249"/>
+      <c r="D14" s="249"/>
+      <c r="E14" s="249"/>
+      <c r="F14" s="249"/>
+      <c r="G14" s="249"/>
+      <c r="H14" s="249"/>
+      <c r="I14" s="249"/>
+      <c r="J14" s="249"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="249"/>
+      <c r="B15" s="249"/>
+      <c r="C15" s="249"/>
+      <c r="D15" s="249"/>
+      <c r="E15" s="249"/>
+      <c r="F15" s="249"/>
+      <c r="G15" s="249"/>
+      <c r="H15" s="249"/>
+      <c r="I15" s="249"/>
+      <c r="J15" s="249"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="249"/>
+      <c r="B16" s="249"/>
+      <c r="C16" s="249"/>
+      <c r="D16" s="249"/>
+      <c r="E16" s="249"/>
+      <c r="F16" s="249"/>
+      <c r="G16" s="249"/>
+      <c r="H16" s="249"/>
+      <c r="I16" s="249"/>
+      <c r="J16" s="249"/>
+    </row>
+    <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="249"/>
+      <c r="B17" s="249"/>
+      <c r="C17" s="249"/>
+      <c r="D17" s="249"/>
+      <c r="E17" s="249"/>
+      <c r="F17" s="249"/>
+      <c r="G17" s="249"/>
+      <c r="H17" s="249"/>
+      <c r="I17" s="249"/>
+      <c r="J17" s="249"/>
+    </row>
+    <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="249"/>
+      <c r="B18" s="249"/>
+      <c r="C18" s="249"/>
+      <c r="D18" s="249"/>
+      <c r="E18" s="249"/>
+      <c r="F18" s="249"/>
+      <c r="G18" s="249"/>
+      <c r="H18" s="249"/>
+      <c r="I18" s="249"/>
+      <c r="J18" s="249"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="H19" s="100"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="250" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="258" t="s">
         <v>328</v>
       </c>
-      <c r="B20" s="250"/>
-      <c r="C20" s="250"/>
-      <c r="D20" s="250"/>
-      <c r="E20" s="250"/>
-      <c r="F20" s="250"/>
-      <c r="G20" s="250"/>
-      <c r="H20" s="250"/>
-      <c r="I20" s="250"/>
-      <c r="J20" s="250"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="250"/>
-      <c r="B21" s="250"/>
-      <c r="C21" s="250"/>
-      <c r="D21" s="250"/>
-      <c r="E21" s="250"/>
-      <c r="F21" s="250"/>
-      <c r="G21" s="250"/>
-      <c r="H21" s="250"/>
-      <c r="I21" s="250"/>
-      <c r="J21" s="250"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="250"/>
-      <c r="B22" s="250"/>
-      <c r="C22" s="250"/>
-      <c r="D22" s="250"/>
-      <c r="E22" s="250"/>
-      <c r="F22" s="250"/>
-      <c r="G22" s="250"/>
-      <c r="H22" s="250"/>
-      <c r="I22" s="250"/>
-      <c r="J22" s="250"/>
-    </row>
-    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="258"/>
+      <c r="C20" s="258"/>
+      <c r="D20" s="258"/>
+      <c r="E20" s="258"/>
+      <c r="F20" s="258"/>
+      <c r="G20" s="258"/>
+      <c r="H20" s="258"/>
+      <c r="I20" s="258"/>
+      <c r="J20" s="258"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="258"/>
+      <c r="B21" s="258"/>
+      <c r="C21" s="258"/>
+      <c r="D21" s="258"/>
+      <c r="E21" s="258"/>
+      <c r="F21" s="258"/>
+      <c r="G21" s="258"/>
+      <c r="H21" s="258"/>
+      <c r="I21" s="258"/>
+      <c r="J21" s="258"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="258"/>
+      <c r="B22" s="258"/>
+      <c r="C22" s="258"/>
+      <c r="D22" s="258"/>
+      <c r="E22" s="258"/>
+      <c r="F22" s="258"/>
+      <c r="G22" s="258"/>
+      <c r="H22" s="258"/>
+      <c r="I22" s="258"/>
+      <c r="J22" s="258"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H23" s="100"/>
     </row>
-    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>19</v>
       </c>
@@ -2895,7 +2898,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="50" t="s">
         <v>238</v>
       </c>
@@ -2909,7 +2912,7 @@
       <c r="I25" s="101"/>
       <c r="J25" s="101"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>45</v>
       </c>
@@ -2925,7 +2928,7 @@
       <c r="I26" s="58"/>
       <c r="J26" s="58"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>241</v>
       </c>
@@ -2941,7 +2944,7 @@
       <c r="I27" s="58"/>
       <c r="J27" s="58"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>239</v>
       </c>
@@ -2958,7 +2961,7 @@
       <c r="I28" s="58"/>
       <c r="J28" s="58"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>240</v>
       </c>
@@ -2974,7 +2977,7 @@
       <c r="I29" s="58"/>
       <c r="J29" s="58"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>316</v>
       </c>
@@ -2990,7 +2993,7 @@
       <c r="I30" s="58"/>
       <c r="J30" s="58"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>242</v>
       </c>
@@ -3006,7 +3009,7 @@
       <c r="I31" s="58"/>
       <c r="J31" s="58"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="99" t="s">
         <v>171</v>
       </c>
@@ -3023,7 +3026,7 @@
       <c r="I32" s="98"/>
       <c r="J32" s="98"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="50" t="s">
         <v>237</v>
       </c>
@@ -3037,7 +3040,7 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>45</v>
       </c>
@@ -3053,7 +3056,7 @@
       <c r="I34" s="58"/>
       <c r="J34" s="58"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>312</v>
       </c>
@@ -3067,7 +3070,7 @@
       <c r="I35" s="58"/>
       <c r="J35" s="58"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>241</v>
       </c>
@@ -3084,7 +3087,7 @@
       <c r="I36" s="58"/>
       <c r="J36" s="58"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>239</v>
       </c>
@@ -3101,7 +3104,7 @@
       <c r="I37" s="58"/>
       <c r="J37" s="58"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>240</v>
       </c>
@@ -3118,7 +3121,7 @@
       <c r="I38" s="58"/>
       <c r="J38" s="58"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>316</v>
       </c>
@@ -3135,7 +3138,7 @@
       <c r="I39" s="58"/>
       <c r="J39" s="58"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>242</v>
       </c>
@@ -3151,7 +3154,7 @@
       <c r="I40" s="58"/>
       <c r="J40" s="58"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="99" t="s">
         <v>171</v>
       </c>
@@ -3168,7 +3171,7 @@
       <c r="I41" s="98"/>
       <c r="J41" s="98"/>
     </row>
-    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="33" t="s">
         <v>1</v>
       </c>
@@ -3211,7 +3214,7 @@
         <v>1522551.4</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="32" t="s">
         <v>34</v>
       </c>
@@ -3234,7 +3237,7 @@
       </c>
       <c r="L43" s="69"/>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="32"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -3255,7 +3258,7 @@
       </c>
       <c r="L44" s="69"/>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="32"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -3268,7 +3271,7 @@
       <c r="J45" s="6"/>
       <c r="L45" s="69"/>
     </row>
-    <row r="46" spans="1:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="32"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -3281,7 +3284,7 @@
       <c r="J46" s="6"/>
       <c r="L46" s="69"/>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="33" t="s">
         <v>40</v>
       </c>
@@ -3312,7 +3315,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="32" t="s">
         <v>253</v>
       </c>
@@ -3333,7 +3336,7 @@
       </c>
       <c r="L48" s="69"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -3349,7 +3352,7 @@
       <c r="J49" s="58"/>
       <c r="L49" s="69"/>
     </row>
-    <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -3365,7 +3368,7 @@
       <c r="J50" s="58"/>
       <c r="L50" s="69"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="32"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -3384,7 +3387,7 @@
       </c>
       <c r="L51" s="69"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="33" t="s">
         <v>35</v>
       </c>
@@ -3412,7 +3415,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="32" t="s">
         <v>247</v>
       </c>
@@ -3427,7 +3430,7 @@
       <c r="J53" s="49"/>
       <c r="L53" s="69"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="35" t="s">
         <v>250</v>
       </c>
@@ -3442,7 +3445,7 @@
       <c r="J54" s="49"/>
       <c r="L54" s="69"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="35" t="s">
         <v>252</v>
       </c>
@@ -3457,7 +3460,7 @@
       <c r="J55" s="49"/>
       <c r="L55" s="69"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="35" t="s">
         <v>251</v>
       </c>
@@ -3472,7 +3475,7 @@
       <c r="J56" s="49"/>
       <c r="L56" s="69"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="33" t="s">
         <v>249</v>
       </c>
@@ -3515,7 +3518,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="32" t="s">
         <v>2</v>
       </c>
@@ -3530,7 +3533,7 @@
       <c r="J58" s="6"/>
       <c r="L58" s="69"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>243</v>
       </c>
@@ -3549,7 +3552,7 @@
       <c r="J59" s="6"/>
       <c r="L59" s="69"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>297</v>
       </c>
@@ -3568,7 +3571,7 @@
       <c r="J60" s="6"/>
       <c r="L60" s="69"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="33" t="s">
         <v>248</v>
       </c>
@@ -3611,7 +3614,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="32" t="s">
         <v>230</v>
       </c>
@@ -3626,7 +3629,7 @@
       <c r="J62" s="36"/>
       <c r="L62" s="69"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
         <v>234</v>
       </c>
@@ -3667,7 +3670,7 @@
       </c>
       <c r="L63" s="69"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
         <v>235</v>
       </c>
@@ -3708,7 +3711,7 @@
       </c>
       <c r="L64" s="69"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>236</v>
       </c>
@@ -3749,7 +3752,7 @@
       </c>
       <c r="L65" s="69"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="33" t="s">
         <v>3</v>
       </c>
@@ -3792,7 +3795,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="32" t="s">
         <v>4</v>
       </c>
@@ -3807,7 +3810,7 @@
       <c r="J67" s="6"/>
       <c r="L67" s="69"/>
     </row>
-    <row r="68" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="71" t="s">
         <v>244</v>
       </c>
@@ -3859,7 +3862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="71" t="s">
         <v>244</v>
       </c>
@@ -3905,7 +3908,7 @@
       <c r="M69" s="86"/>
       <c r="N69" s="86"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>245</v>
       </c>
@@ -3951,7 +3954,7 @@
       <c r="M70" s="86"/>
       <c r="N70" s="86"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
         <v>245</v>
       </c>
@@ -3997,7 +4000,7 @@
       <c r="M71" s="86"/>
       <c r="N71" s="86"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>246</v>
       </c>
@@ -4035,7 +4038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
         <v>330</v>
       </c>
@@ -4066,7 +4069,7 @@
       <c r="M73" s="86"/>
       <c r="N73" s="86"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="35" t="s">
         <v>300</v>
       </c>
@@ -4103,7 +4106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="35" t="s">
         <v>282</v>
       </c>
@@ -4155,7 +4158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="35" t="s">
         <v>282</v>
       </c>
@@ -4207,7 +4210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="35" t="s">
         <v>283</v>
       </c>
@@ -4259,7 +4262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="35" t="s">
         <v>283</v>
       </c>
@@ -4308,7 +4311,7 @@
       </c>
       <c r="N78" s="86"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="35" t="s">
         <v>283</v>
       </c>
@@ -4360,7 +4363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="156" t="s">
         <v>281</v>
       </c>
@@ -4393,7 +4396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="156"/>
       <c r="B81" s="154"/>
       <c r="C81" s="154"/>
@@ -4418,10 +4421,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="248"/>
-      <c r="B82" s="249"/>
-      <c r="C82" s="251"/>
+    <row r="82" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="256"/>
+      <c r="B82" s="257"/>
+      <c r="C82" s="259"/>
       <c r="D82" s="44"/>
       <c r="E82" s="68"/>
       <c r="F82" s="68"/>
@@ -4443,10 +4446,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="248"/>
-      <c r="B83" s="249"/>
-      <c r="C83" s="251"/>
+    <row r="83" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="256"/>
+      <c r="B83" s="257"/>
+      <c r="C83" s="259"/>
       <c r="D83" s="44"/>
       <c r="E83" s="68"/>
       <c r="F83" s="68"/>
@@ -4468,7 +4471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="152"/>
       <c r="B84" s="153"/>
       <c r="C84" s="84"/>
@@ -4493,7 +4496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="144"/>
       <c r="B85" s="144"/>
       <c r="C85" s="155"/>
@@ -4521,7 +4524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="71"/>
       <c r="B86" s="72"/>
       <c r="C86" s="72"/>
@@ -4539,7 +4542,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="33" t="s">
         <v>5</v>
       </c>
@@ -4586,7 +4589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -4599,7 +4602,7 @@
       <c r="J88" s="6"/>
       <c r="L88" s="69"/>
     </row>
-    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -4612,7 +4615,7 @@
       <c r="J89" s="6"/>
       <c r="L89" s="69"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="32" t="s">
         <v>231</v>
       </c>
@@ -4627,7 +4630,7 @@
       <c r="J90" s="6"/>
       <c r="L90" s="69"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
         <v>331</v>
       </c>
@@ -4665,7 +4668,7 @@
       <c r="K91" s="74"/>
       <c r="L91" s="69"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="6"/>
       <c r="B92" s="35"/>
       <c r="C92" s="6"/>
@@ -4682,7 +4685,7 @@
       <c r="K92" s="74"/>
       <c r="L92" s="69"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
       <c r="B93" s="35"/>
       <c r="C93" s="6"/>
@@ -4696,7 +4699,7 @@
       <c r="K93" s="74"/>
       <c r="L93" s="69"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="6"/>
       <c r="B94" s="35"/>
       <c r="C94" s="6"/>
@@ -4710,7 +4713,7 @@
       <c r="K94" s="74"/>
       <c r="L94" s="69"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
       <c r="B95" s="35"/>
       <c r="C95" s="6"/>
@@ -4724,7 +4727,7 @@
       <c r="K95" s="74"/>
       <c r="L95" s="69"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -4738,7 +4741,7 @@
       <c r="L96" s="69"/>
       <c r="M96" s="43"/>
     </row>
-    <row r="97" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="33" t="s">
         <v>232</v>
       </c>
@@ -4782,7 +4785,7 @@
       </c>
       <c r="N97" s="43"/>
     </row>
-    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -4795,7 +4798,7 @@
       <c r="J98" s="6"/>
       <c r="L98" s="69"/>
     </row>
-    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -4808,7 +4811,7 @@
       <c r="J99" s="6"/>
       <c r="L99" s="69"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="32" t="s">
         <v>6</v>
       </c>
@@ -4823,7 +4826,7 @@
       <c r="J100" s="6"/>
       <c r="L100" s="69"/>
     </row>
-    <row r="101" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
         <v>7</v>
       </c>
@@ -4862,7 +4865,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="32"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -4876,7 +4879,7 @@
       <c r="L102" s="69"/>
       <c r="N102" s="44"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -4890,7 +4893,7 @@
       <c r="L103" s="69"/>
       <c r="N103" s="43"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="33" t="s">
         <v>8</v>
       </c>
@@ -4934,7 +4937,7 @@
       </c>
       <c r="N104" s="43"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
         <v>28</v>
       </c>
@@ -4969,7 +4972,7 @@
       </c>
       <c r="L105" s="69"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
         <v>29</v>
       </c>
@@ -5002,7 +5005,7 @@
       </c>
       <c r="L106" s="69"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="33" t="s">
         <v>233</v>
       </c>
@@ -5045,7 +5048,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="104"/>
       <c r="B108" s="104"/>
       <c r="C108" s="104"/>
@@ -5058,7 +5061,7 @@
       <c r="J108" s="104"/>
       <c r="L108" s="69"/>
     </row>
-    <row r="109" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="106" t="s">
         <v>46</v>
       </c>
@@ -5101,7 +5104,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="109"/>
       <c r="B110" s="110"/>
       <c r="C110" s="110"/>
@@ -5115,7 +5118,7 @@
       <c r="K110" s="43"/>
       <c r="L110" s="69"/>
     </row>
-    <row r="111" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>30</v>
       </c>
@@ -5162,7 +5165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D112" s="89"/>
       <c r="E112" s="43"/>
       <c r="F112" s="43"/>
@@ -5170,7 +5173,7 @@
       <c r="H112" s="43"/>
       <c r="I112" s="43"/>
     </row>
-    <row r="113" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="64" t="s">
         <v>41</v>
       </c>
@@ -5182,7 +5185,7 @@
       <c r="H113" s="43"/>
       <c r="I113" s="43"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>343</v>
       </c>
@@ -5195,7 +5198,7 @@
       <c r="H114" s="43"/>
       <c r="I114" s="43"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>344</v>
       </c>
@@ -5208,7 +5211,7 @@
       <c r="H115" s="43"/>
       <c r="I115" s="43"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>345</v>
       </c>
@@ -5221,7 +5224,7 @@
       <c r="H116" s="43"/>
       <c r="I116" s="43"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>346</v>
       </c>
@@ -5234,7 +5237,7 @@
       <c r="H117" s="43"/>
       <c r="I117" s="43"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>347</v>
       </c>
@@ -5247,7 +5250,7 @@
       <c r="H118" s="43"/>
       <c r="I118" s="43"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>348</v>
       </c>
@@ -5260,7 +5263,7 @@
       <c r="H119" s="43"/>
       <c r="I119" s="43"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>349</v>
       </c>
@@ -5273,7 +5276,7 @@
       <c r="H120" s="43"/>
       <c r="I120" s="43"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>352</v>
       </c>
@@ -5286,7 +5289,7 @@
       <c r="H121" s="43"/>
       <c r="I121" s="43"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>351</v>
       </c>
@@ -5300,7 +5303,7 @@
       <c r="H122" s="43"/>
       <c r="I122" s="43"/>
     </row>
-    <row r="123" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>350</v>
       </c>
@@ -5314,7 +5317,7 @@
       <c r="H123" s="43"/>
       <c r="I123" s="43"/>
     </row>
-    <row r="124" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="65" t="s">
         <v>17</v>
       </c>
@@ -5329,27 +5332,27 @@
       <c r="H124" s="43"/>
       <c r="I124" s="43"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E125" s="43"/>
       <c r="F125" s="43"/>
       <c r="G125" s="43"/>
       <c r="H125" s="43"/>
       <c r="I125" s="43"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E126" s="60"/>
       <c r="F126" s="60"/>
       <c r="G126" s="60"/>
       <c r="H126" s="60"/>
       <c r="I126" s="60"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A127" s="246" t="s">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" s="254" t="s">
         <v>36</v>
       </c>
-      <c r="B127" s="247"/>
-      <c r="C127" s="247"/>
-      <c r="D127" s="247"/>
+      <c r="B127" s="255"/>
+      <c r="C127" s="255"/>
+      <c r="D127" s="255"/>
       <c r="E127" s="82" t="s">
         <v>11</v>
       </c>
@@ -5369,9 +5372,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="248"/>
-      <c r="B128" s="249"/>
+    <row r="128" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="256"/>
+      <c r="B128" s="257"/>
       <c r="C128" s="84"/>
       <c r="D128" s="44"/>
       <c r="E128" s="68">
@@ -5384,9 +5387,9 @@
       <c r="I128" s="68"/>
       <c r="J128" s="58"/>
     </row>
-    <row r="129" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="248"/>
-      <c r="B129" s="249"/>
+    <row r="129" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="256"/>
+      <c r="B129" s="257"/>
       <c r="C129" s="84"/>
       <c r="D129" s="44"/>
       <c r="E129" s="68"/>
@@ -5396,12 +5399,12 @@
       <c r="I129" s="68"/>
       <c r="J129" s="58"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A130" s="243" t="s">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" s="251" t="s">
         <v>17</v>
       </c>
-      <c r="B130" s="244"/>
-      <c r="C130" s="245"/>
+      <c r="B130" s="252"/>
+      <c r="C130" s="253"/>
       <c r="D130" s="81">
         <f>SUM(D128:D129)</f>
         <v>0</v>
@@ -5427,14 +5430,14 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E132" s="43"/>
       <c r="F132" s="43"/>
       <c r="G132" s="43"/>
       <c r="H132" s="43"/>
       <c r="I132" s="43"/>
     </row>
-    <row r="133" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="38" t="s">
         <v>31</v>
       </c>
@@ -5443,7 +5446,7 @@
         <v>11000000</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="40" t="s">
         <v>33</v>
       </c>
@@ -5451,37 +5454,37 @@
         <f>D111-D109</f>
         <v>9608383.8599999994</v>
       </c>
-      <c r="D134" s="252" t="s">
+      <c r="D134" s="260" t="s">
         <v>323</v>
       </c>
-      <c r="E134" s="252"/>
-      <c r="F134" s="252"/>
-      <c r="G134" s="252"/>
-      <c r="H134" s="252"/>
-      <c r="I134" s="252"/>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D135" s="252"/>
-      <c r="E135" s="252"/>
-      <c r="F135" s="252"/>
-      <c r="G135" s="252"/>
-      <c r="H135" s="252"/>
-      <c r="I135" s="252"/>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E134" s="260"/>
+      <c r="F134" s="260"/>
+      <c r="G134" s="260"/>
+      <c r="H134" s="260"/>
+      <c r="I134" s="260"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D135" s="260"/>
+      <c r="E135" s="260"/>
+      <c r="F135" s="260"/>
+      <c r="G135" s="260"/>
+      <c r="H135" s="260"/>
+      <c r="I135" s="260"/>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B136" s="17"/>
       <c r="C136" s="18"/>
-      <c r="D136" s="252"/>
-      <c r="E136" s="252"/>
-      <c r="F136" s="252"/>
-      <c r="G136" s="252"/>
-      <c r="H136" s="252"/>
-      <c r="I136" s="252"/>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D136" s="260"/>
+      <c r="E136" s="260"/>
+      <c r="F136" s="260"/>
+      <c r="G136" s="260"/>
+      <c r="H136" s="260"/>
+      <c r="I136" s="260"/>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="19" t="s">
         <v>21</v>
       </c>
@@ -5489,14 +5492,14 @@
         <v>-1505552.0204280028</v>
       </c>
       <c r="C137" s="20"/>
-      <c r="D137" s="252"/>
-      <c r="E137" s="252"/>
-      <c r="F137" s="252"/>
-      <c r="G137" s="252"/>
-      <c r="H137" s="252"/>
-      <c r="I137" s="252"/>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D137" s="260"/>
+      <c r="E137" s="260"/>
+      <c r="F137" s="260"/>
+      <c r="G137" s="260"/>
+      <c r="H137" s="260"/>
+      <c r="I137" s="260"/>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="21" t="s">
         <v>22</v>
       </c>
@@ -5507,14 +5510,14 @@
       <c r="C138" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D138" s="252"/>
-      <c r="E138" s="252"/>
-      <c r="F138" s="252"/>
-      <c r="G138" s="252"/>
-      <c r="H138" s="252"/>
-      <c r="I138" s="252"/>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D138" s="260"/>
+      <c r="E138" s="260"/>
+      <c r="F138" s="260"/>
+      <c r="G138" s="260"/>
+      <c r="H138" s="260"/>
+      <c r="I138" s="260"/>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="21" t="s">
         <v>38</v>
       </c>
@@ -5523,15 +5526,15 @@
         <v>-9608383.8599999994</v>
       </c>
       <c r="C139" s="18"/>
-      <c r="D139" s="252"/>
-      <c r="E139" s="252"/>
-      <c r="F139" s="252"/>
-      <c r="G139" s="252"/>
-      <c r="H139" s="252"/>
-      <c r="I139" s="252"/>
+      <c r="D139" s="260"/>
+      <c r="E139" s="260"/>
+      <c r="F139" s="260"/>
+      <c r="G139" s="260"/>
+      <c r="H139" s="260"/>
+      <c r="I139" s="260"/>
       <c r="K139" s="44"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="21" t="s">
         <v>37</v>
       </c>
@@ -5540,32 +5543,32 @@
         <v>0</v>
       </c>
       <c r="C140" s="18"/>
-      <c r="D140" s="252"/>
-      <c r="E140" s="252"/>
-      <c r="F140" s="252"/>
-      <c r="G140" s="252"/>
-      <c r="H140" s="252"/>
-      <c r="I140" s="252"/>
+      <c r="D140" s="260"/>
+      <c r="E140" s="260"/>
+      <c r="F140" s="260"/>
+      <c r="G140" s="260"/>
+      <c r="H140" s="260"/>
+      <c r="I140" s="260"/>
       <c r="K140" s="52"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="21" t="s">
         <v>311</v>
       </c>
       <c r="B141" s="30">
         <f>B151</f>
-        <v>0</v>
+        <v>339557.28</v>
       </c>
       <c r="C141" s="18"/>
-      <c r="D141" s="252"/>
-      <c r="E141" s="252"/>
-      <c r="F141" s="252"/>
-      <c r="G141" s="252"/>
-      <c r="H141" s="252"/>
-      <c r="I141" s="252"/>
+      <c r="D141" s="260"/>
+      <c r="E141" s="260"/>
+      <c r="F141" s="260"/>
+      <c r="G141" s="260"/>
+      <c r="H141" s="260"/>
+      <c r="I141" s="260"/>
       <c r="K141" s="52"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="21" t="s">
         <v>32</v>
       </c>
@@ -5574,14 +5577,14 @@
         <v>0</v>
       </c>
       <c r="C142" s="22"/>
-      <c r="D142" s="252"/>
-      <c r="E142" s="252"/>
-      <c r="F142" s="252"/>
-      <c r="G142" s="252"/>
-      <c r="H142" s="252"/>
-      <c r="I142" s="252"/>
-    </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D142" s="260"/>
+      <c r="E142" s="260"/>
+      <c r="F142" s="260"/>
+      <c r="G142" s="260"/>
+      <c r="H142" s="260"/>
+      <c r="I142" s="260"/>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="21" t="s">
         <v>309</v>
       </c>
@@ -5589,14 +5592,14 @@
         <v>0</v>
       </c>
       <c r="C143" s="22"/>
-      <c r="D143" s="252"/>
-      <c r="E143" s="252"/>
-      <c r="F143" s="252"/>
-      <c r="G143" s="252"/>
-      <c r="H143" s="252"/>
-      <c r="I143" s="252"/>
-    </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D143" s="260"/>
+      <c r="E143" s="260"/>
+      <c r="F143" s="260"/>
+      <c r="G143" s="260"/>
+      <c r="H143" s="260"/>
+      <c r="I143" s="260"/>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="21" t="s">
         <v>41</v>
       </c>
@@ -5605,14 +5608,14 @@
         <v>-206000</v>
       </c>
       <c r="C144" s="22"/>
-      <c r="D144" s="252"/>
-      <c r="E144" s="252"/>
-      <c r="F144" s="252"/>
-      <c r="G144" s="252"/>
-      <c r="H144" s="252"/>
-      <c r="I144" s="252"/>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D144" s="260"/>
+      <c r="E144" s="260"/>
+      <c r="F144" s="260"/>
+      <c r="G144" s="260"/>
+      <c r="H144" s="260"/>
+      <c r="I144" s="260"/>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="21" t="s">
         <v>342</v>
       </c>
@@ -5620,86 +5623,90 @@
         <v>400000</v>
       </c>
       <c r="C145" s="22"/>
-      <c r="D145" s="252"/>
-      <c r="E145" s="252"/>
-      <c r="F145" s="252"/>
-      <c r="G145" s="252"/>
-      <c r="H145" s="252"/>
-      <c r="I145" s="252"/>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D145" s="260"/>
+      <c r="E145" s="260"/>
+      <c r="F145" s="260"/>
+      <c r="G145" s="260"/>
+      <c r="H145" s="260"/>
+      <c r="I145" s="260"/>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="19" t="s">
         <v>24</v>
       </c>
       <c r="B146" s="23">
         <f>SUM(B137:B145)</f>
-        <v>-979600.31345474347</v>
+        <v>-640043.03345474345</v>
       </c>
       <c r="C146" s="70"/>
-      <c r="D146" s="252"/>
-      <c r="E146" s="252"/>
-      <c r="F146" s="252"/>
-      <c r="G146" s="252"/>
-      <c r="H146" s="252"/>
-      <c r="I146" s="252"/>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D146" s="260"/>
+      <c r="E146" s="260"/>
+      <c r="F146" s="260"/>
+      <c r="G146" s="260"/>
+      <c r="H146" s="260"/>
+      <c r="I146" s="260"/>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="22"/>
       <c r="C147" s="18"/>
-      <c r="D147" s="252"/>
-      <c r="E147" s="252"/>
-      <c r="F147" s="252"/>
-      <c r="G147" s="252"/>
-      <c r="H147" s="252"/>
-      <c r="I147" s="252"/>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D147" s="260"/>
+      <c r="E147" s="260"/>
+      <c r="F147" s="260"/>
+      <c r="G147" s="260"/>
+      <c r="H147" s="260"/>
+      <c r="I147" s="260"/>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="16" t="s">
         <v>310</v>
       </c>
       <c r="B148" s="8"/>
       <c r="C148" s="18"/>
-      <c r="D148" s="252"/>
-      <c r="E148" s="252"/>
-      <c r="F148" s="252"/>
-      <c r="G148" s="252"/>
-      <c r="H148" s="252"/>
-      <c r="I148" s="252"/>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A149" s="19"/>
-      <c r="B149" s="31"/>
+      <c r="D148" s="260"/>
+      <c r="E148" s="260"/>
+      <c r="F148" s="260"/>
+      <c r="G148" s="260"/>
+      <c r="H148" s="260"/>
+      <c r="I148" s="260"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="B149" s="31">
+        <v>339557.28</v>
+      </c>
       <c r="C149" s="18"/>
       <c r="D149" s="25"/>
     </row>
-    <row r="150" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="179"/>
       <c r="B150" s="30"/>
       <c r="C150" s="18"/>
       <c r="D150" s="25"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="36" t="s">
         <v>17</v>
       </c>
       <c r="B151" s="37">
         <f>SUM(B148:B150)</f>
-        <v>0</v>
+        <v>339557.28</v>
       </c>
       <c r="C151" s="18"/>
       <c r="D151" s="25"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="22"/>
       <c r="C152" s="18"/>
       <c r="D152" s="25"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="22"/>
       <c r="C153" s="18"/>
       <c r="D153" s="25"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C154" s="18"/>
       <c r="D154" s="43"/>
       <c r="E154" s="86"/>
@@ -5708,7 +5715,7 @@
       <c r="H154" s="86"/>
       <c r="I154" s="86"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="16" t="s">
         <v>25</v>
       </c>
@@ -5724,7 +5731,7 @@
       <c r="I155" s="86"/>
       <c r="J155" s="86"/>
     </row>
-    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="19" t="s">
         <v>260</v>
       </c>
@@ -5737,7 +5744,7 @@
       <c r="H156" s="93"/>
       <c r="I156" s="93"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="19"/>
       <c r="B157" s="85"/>
       <c r="C157" s="24"/>
@@ -5747,7 +5754,7 @@
       <c r="H157" s="43"/>
       <c r="I157" s="43"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="36" t="s">
         <v>17</v>
       </c>
@@ -5757,62 +5764,62 @@
       </c>
       <c r="C158" s="24"/>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C159" s="25"/>
       <c r="D159" s="86"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B160" s="22"/>
       <c r="C160" s="18"/>
     </row>
-    <row r="162" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:18" x14ac:dyDescent="0.25">
       <c r="R162" s="9"/>
     </row>
-    <row r="165" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B165" s="242"/>
-      <c r="C165" s="242"/>
-      <c r="D165" s="242"/>
-      <c r="E165" s="242"/>
+    <row r="165" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B165" s="250"/>
+      <c r="C165" s="250"/>
+      <c r="D165" s="250"/>
+      <c r="E165" s="250"/>
       <c r="F165" s="95"/>
       <c r="G165" s="95"/>
       <c r="H165" s="95"/>
       <c r="I165" s="95"/>
     </row>
-    <row r="166" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B166" s="242"/>
-      <c r="C166" s="242"/>
-      <c r="D166" s="242"/>
-      <c r="E166" s="242"/>
+    <row r="166" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B166" s="250"/>
+      <c r="C166" s="250"/>
+      <c r="D166" s="250"/>
+      <c r="E166" s="250"/>
       <c r="F166" s="95"/>
       <c r="G166" s="95"/>
       <c r="H166" s="95"/>
       <c r="I166" s="95"/>
     </row>
-    <row r="167" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B167" s="242"/>
-      <c r="C167" s="242"/>
-      <c r="D167" s="242"/>
-      <c r="E167" s="242"/>
+    <row r="167" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B167" s="250"/>
+      <c r="C167" s="250"/>
+      <c r="D167" s="250"/>
+      <c r="E167" s="250"/>
       <c r="F167" s="95"/>
       <c r="G167" s="95"/>
       <c r="H167" s="95"/>
       <c r="I167" s="95"/>
     </row>
-    <row r="168" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B168" s="242"/>
-      <c r="C168" s="242"/>
-      <c r="D168" s="242"/>
-      <c r="E168" s="242"/>
+    <row r="168" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B168" s="250"/>
+      <c r="C168" s="250"/>
+      <c r="D168" s="250"/>
+      <c r="E168" s="250"/>
       <c r="F168" s="95"/>
       <c r="G168" s="95"/>
       <c r="H168" s="95"/>
       <c r="I168" s="95"/>
     </row>
-    <row r="169" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B169" s="242"/>
-      <c r="C169" s="242"/>
-      <c r="D169" s="242"/>
-      <c r="E169" s="242"/>
+    <row r="169" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B169" s="250"/>
+      <c r="C169" s="250"/>
+      <c r="D169" s="250"/>
+      <c r="E169" s="250"/>
       <c r="F169" s="95"/>
       <c r="G169" s="95"/>
       <c r="H169" s="95"/>
@@ -5840,27 +5847,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DI154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" customWidth="1"/>
-    <col min="4" max="4" width="42.6640625" customWidth="1"/>
-    <col min="5" max="5" width="36.44140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="4" max="4" width="42.7109375" customWidth="1"/>
+    <col min="5" max="5" width="36.42578125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="13.6640625" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="180"/>
       <c r="B1" s="181"/>
       <c r="C1" s="181"/>
@@ -5876,15 +5883,15 @@
       <c r="K1" s="181" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="262">
+      <c r="L1" s="266">
         <f>RESUMEN!D111-RESUMEN!D109</f>
         <v>9608383.8599999994</v>
       </c>
-      <c r="M1" s="263"/>
+      <c r="M1" s="267"/>
       <c r="N1" s="182"/>
       <c r="O1" s="59"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="183"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -5907,7 +5914,7 @@
       <c r="N2" s="185"/>
       <c r="O2" s="59"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="183" t="str">
         <f>RESUMEN!C5</f>
         <v>PERÍODO: OCTUBRE</v>
@@ -5929,7 +5936,7 @@
       <c r="N3" s="188"/>
       <c r="O3" s="15"/>
     </row>
-    <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="189"/>
       <c r="B4" s="190"/>
       <c r="C4" s="190"/>
@@ -5946,188 +5953,188 @@
       <c r="N4" s="193"/>
       <c r="O4" s="15"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="271" t="s">
+      <c r="C5" s="275" t="s">
         <v>337</v>
       </c>
-      <c r="D5" s="272"/>
-      <c r="E5" s="272"/>
-      <c r="F5" s="272"/>
-      <c r="G5" s="272"/>
-      <c r="H5" s="272"/>
-      <c r="I5" s="272"/>
-      <c r="J5" s="272"/>
-      <c r="K5" s="272"/>
-      <c r="L5" s="272"/>
-      <c r="M5" s="272"/>
-      <c r="N5" s="273"/>
+      <c r="D5" s="276"/>
+      <c r="E5" s="276"/>
+      <c r="F5" s="276"/>
+      <c r="G5" s="276"/>
+      <c r="H5" s="276"/>
+      <c r="I5" s="276"/>
+      <c r="J5" s="276"/>
+      <c r="K5" s="276"/>
+      <c r="L5" s="276"/>
+      <c r="M5" s="276"/>
+      <c r="N5" s="277"/>
       <c r="O5" s="15"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="274"/>
-      <c r="D6" s="275"/>
-      <c r="E6" s="275"/>
-      <c r="F6" s="275"/>
-      <c r="G6" s="275"/>
-      <c r="H6" s="275"/>
-      <c r="I6" s="275"/>
-      <c r="J6" s="275"/>
-      <c r="K6" s="275"/>
-      <c r="L6" s="275"/>
-      <c r="M6" s="275"/>
-      <c r="N6" s="276"/>
+      <c r="C6" s="278"/>
+      <c r="D6" s="279"/>
+      <c r="E6" s="279"/>
+      <c r="F6" s="279"/>
+      <c r="G6" s="279"/>
+      <c r="H6" s="279"/>
+      <c r="I6" s="279"/>
+      <c r="J6" s="279"/>
+      <c r="K6" s="279"/>
+      <c r="L6" s="279"/>
+      <c r="M6" s="279"/>
+      <c r="N6" s="280"/>
       <c r="O6" s="15"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="274"/>
-      <c r="D7" s="275"/>
-      <c r="E7" s="275"/>
-      <c r="F7" s="275"/>
-      <c r="G7" s="275"/>
-      <c r="H7" s="275"/>
-      <c r="I7" s="275"/>
-      <c r="J7" s="275"/>
-      <c r="K7" s="275"/>
-      <c r="L7" s="275"/>
-      <c r="M7" s="275"/>
-      <c r="N7" s="276"/>
+      <c r="C7" s="278"/>
+      <c r="D7" s="279"/>
+      <c r="E7" s="279"/>
+      <c r="F7" s="279"/>
+      <c r="G7" s="279"/>
+      <c r="H7" s="279"/>
+      <c r="I7" s="279"/>
+      <c r="J7" s="279"/>
+      <c r="K7" s="279"/>
+      <c r="L7" s="279"/>
+      <c r="M7" s="279"/>
+      <c r="N7" s="280"/>
       <c r="O7" s="15"/>
     </row>
-    <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="277"/>
-      <c r="D8" s="278"/>
-      <c r="E8" s="278"/>
-      <c r="F8" s="278"/>
-      <c r="G8" s="278"/>
-      <c r="H8" s="278"/>
-      <c r="I8" s="278"/>
-      <c r="J8" s="278"/>
-      <c r="K8" s="278"/>
-      <c r="L8" s="278"/>
-      <c r="M8" s="278"/>
-      <c r="N8" s="279"/>
+      <c r="C8" s="281"/>
+      <c r="D8" s="282"/>
+      <c r="E8" s="282"/>
+      <c r="F8" s="282"/>
+      <c r="G8" s="282"/>
+      <c r="H8" s="282"/>
+      <c r="I8" s="282"/>
+      <c r="J8" s="282"/>
+      <c r="K8" s="282"/>
+      <c r="L8" s="282"/>
+      <c r="M8" s="282"/>
+      <c r="N8" s="283"/>
       <c r="P8" s="86">
         <f>L1-K133</f>
         <v>-1338773.6948400009</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="280" t="s">
+      <c r="C9" s="284" t="s">
         <v>355</v>
       </c>
-      <c r="D9" s="281"/>
-      <c r="E9" s="281"/>
-      <c r="F9" s="281"/>
-      <c r="G9" s="281"/>
-      <c r="H9" s="281"/>
-      <c r="I9" s="281"/>
-      <c r="J9" s="281"/>
-      <c r="K9" s="281"/>
-      <c r="L9" s="281"/>
-      <c r="M9" s="281"/>
-      <c r="N9" s="282"/>
+      <c r="D9" s="285"/>
+      <c r="E9" s="285"/>
+      <c r="F9" s="285"/>
+      <c r="G9" s="285"/>
+      <c r="H9" s="285"/>
+      <c r="I9" s="285"/>
+      <c r="J9" s="285"/>
+      <c r="K9" s="285"/>
+      <c r="L9" s="285"/>
+      <c r="M9" s="285"/>
+      <c r="N9" s="286"/>
       <c r="P9" s="86"/>
     </row>
-    <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="283"/>
-      <c r="D10" s="284"/>
-      <c r="E10" s="284"/>
-      <c r="F10" s="284"/>
-      <c r="G10" s="284"/>
-      <c r="H10" s="284"/>
-      <c r="I10" s="284"/>
-      <c r="J10" s="284"/>
-      <c r="K10" s="284"/>
-      <c r="L10" s="284"/>
-      <c r="M10" s="284"/>
-      <c r="N10" s="285"/>
+      <c r="C10" s="287"/>
+      <c r="D10" s="288"/>
+      <c r="E10" s="288"/>
+      <c r="F10" s="288"/>
+      <c r="G10" s="288"/>
+      <c r="H10" s="288"/>
+      <c r="I10" s="288"/>
+      <c r="J10" s="288"/>
+      <c r="K10" s="288"/>
+      <c r="L10" s="288"/>
+      <c r="M10" s="288"/>
+      <c r="N10" s="289"/>
       <c r="P10" s="86"/>
     </row>
-    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="253" t="s">
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="262" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="255" t="s">
+      <c r="B11" s="290" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="253" t="s">
+      <c r="C11" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="257" t="s">
+      <c r="D11" s="292" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="257" t="s">
+      <c r="E11" s="292" t="s">
         <v>274</v>
       </c>
-      <c r="F11" s="253" t="s">
+      <c r="F11" s="262" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="253" t="s">
+      <c r="G11" s="262" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="253" t="s">
+      <c r="H11" s="262" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="264" t="s">
+      <c r="I11" s="268" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="266" t="s">
+      <c r="J11" s="270" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="266" t="s">
+      <c r="K11" s="270" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="269" t="s">
+      <c r="L11" s="273" t="s">
         <v>42</v>
       </c>
-      <c r="M11" s="266" t="s">
+      <c r="M11" s="270" t="s">
         <v>285</v>
       </c>
-      <c r="N11" s="266" t="s">
+      <c r="N11" s="270" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="254"/>
-      <c r="B12" s="256"/>
-      <c r="C12" s="254"/>
-      <c r="D12" s="258"/>
-      <c r="E12" s="258"/>
-      <c r="F12" s="254"/>
-      <c r="G12" s="254"/>
-      <c r="H12" s="254"/>
-      <c r="I12" s="265"/>
-      <c r="J12" s="267"/>
-      <c r="K12" s="267"/>
-      <c r="L12" s="270"/>
-      <c r="M12" s="267"/>
-      <c r="N12" s="267"/>
-    </row>
-    <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="254"/>
-      <c r="B13" s="256"/>
-      <c r="C13" s="254"/>
-      <c r="D13" s="258"/>
-      <c r="E13" s="258"/>
-      <c r="F13" s="254"/>
-      <c r="G13" s="254"/>
-      <c r="H13" s="254"/>
-      <c r="I13" s="265"/>
-      <c r="J13" s="267"/>
-      <c r="K13" s="268"/>
-      <c r="L13" s="270"/>
+    <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="263"/>
+      <c r="B12" s="291"/>
+      <c r="C12" s="263"/>
+      <c r="D12" s="293"/>
+      <c r="E12" s="293"/>
+      <c r="F12" s="263"/>
+      <c r="G12" s="263"/>
+      <c r="H12" s="263"/>
+      <c r="I12" s="269"/>
+      <c r="J12" s="271"/>
+      <c r="K12" s="271"/>
+      <c r="L12" s="274"/>
+      <c r="M12" s="271"/>
+      <c r="N12" s="271"/>
+    </row>
+    <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="263"/>
+      <c r="B13" s="291"/>
+      <c r="C13" s="263"/>
+      <c r="D13" s="293"/>
+      <c r="E13" s="293"/>
+      <c r="F13" s="263"/>
+      <c r="G13" s="263"/>
+      <c r="H13" s="263"/>
+      <c r="I13" s="269"/>
+      <c r="J13" s="271"/>
+      <c r="K13" s="272"/>
+      <c r="L13" s="274"/>
       <c r="M13" s="140" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 14/11</v>
@@ -6137,7 +6144,7 @@
         <v>VTO 14/11</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>121</v>
       </c>
@@ -6183,12 +6190,12 @@
         <v>120735.58364424</v>
       </c>
       <c r="O14" s="121"/>
-      <c r="Q14" s="259" t="s">
+      <c r="Q14" s="261" t="s">
         <v>259</v>
       </c>
-      <c r="R14" s="259"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R14" s="261"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="35" t="s">
@@ -6230,10 +6237,10 @@
         <v>143094.02505984006</v>
       </c>
       <c r="O15" s="121"/>
-      <c r="Q15" s="259"/>
-      <c r="R15" s="259"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q15" s="261"/>
+      <c r="R15" s="261"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>121</v>
       </c>
@@ -6285,7 +6292,7 @@
         <v>113901.49400400001</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>121</v>
       </c>
@@ -6337,7 +6344,7 @@
         <v>134994.36326400004</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>121</v>
       </c>
@@ -6389,7 +6396,7 @@
         <v>127611.859023</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="57" t="s">
         <v>123</v>
       </c>
@@ -6445,7 +6452,7 @@
         <v>157141.87598700004</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="57" t="s">
         <v>124</v>
       </c>
@@ -6502,7 +6509,7 @@
         <v>183507.96256200003</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="57" t="s">
         <v>123</v>
       </c>
@@ -6552,7 +6559,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="57" t="s">
         <v>125</v>
       </c>
@@ -6606,7 +6613,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="57" t="s">
         <v>125</v>
       </c>
@@ -6655,7 +6662,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="57" t="s">
         <v>125</v>
       </c>
@@ -6707,7 +6714,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="57" t="s">
         <v>123</v>
       </c>
@@ -6758,7 +6765,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="57" t="s">
         <v>124</v>
       </c>
@@ -6808,7 +6815,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="57" t="s">
         <v>123</v>
       </c>
@@ -6855,7 +6862,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="57" t="s">
         <v>125</v>
       </c>
@@ -6904,7 +6911,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="57" t="s">
         <v>125</v>
       </c>
@@ -6953,7 +6960,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="57" t="s">
         <v>125</v>
       </c>
@@ -7000,7 +7007,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="57" t="s">
         <v>123</v>
       </c>
@@ -7050,7 +7057,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="57" t="s">
         <v>124</v>
       </c>
@@ -7102,7 +7109,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A33" s="57" t="s">
         <v>123</v>
       </c>
@@ -7152,7 +7159,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A34" s="149" t="s">
         <v>125</v>
       </c>
@@ -7202,7 +7209,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="35" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A35" s="57" t="s">
         <v>125</v>
       </c>
@@ -7253,7 +7260,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="36" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A36" s="57" t="s">
         <v>125</v>
       </c>
@@ -7300,7 +7307,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A37" s="57" t="s">
         <v>123</v>
       </c>
@@ -7353,7 +7360,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A38" s="57" t="s">
         <v>124</v>
       </c>
@@ -7403,7 +7410,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="149" t="s">
         <v>123</v>
       </c>
@@ -7551,7 +7558,7 @@
       <c r="DH39" s="74"/>
       <c r="DI39" s="74"/>
     </row>
-    <row r="40" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="149" t="s">
         <v>125</v>
       </c>
@@ -7696,7 +7703,7 @@
       <c r="DH40" s="74"/>
       <c r="DI40" s="74"/>
     </row>
-    <row r="41" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="149" t="s">
         <v>125</v>
       </c>
@@ -7846,7 +7853,7 @@
       <c r="DH41" s="74"/>
       <c r="DI41" s="74"/>
     </row>
-    <row r="42" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="149" t="s">
         <v>125</v>
       </c>
@@ -7991,7 +7998,7 @@
       <c r="DH42" s="74"/>
       <c r="DI42" s="74"/>
     </row>
-    <row r="43" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A43" s="57" t="s">
         <v>123</v>
       </c>
@@ -8041,7 +8048,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A44" s="57" t="s">
         <v>124</v>
       </c>
@@ -8093,7 +8100,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A45" s="57" t="s">
         <v>123</v>
       </c>
@@ -8149,7 +8156,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="46" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A46" s="57" t="s">
         <v>125</v>
       </c>
@@ -8202,7 +8209,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="47" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A47" s="57" t="s">
         <v>125</v>
       </c>
@@ -8254,7 +8261,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="48" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A48" s="57" t="s">
         <v>125</v>
       </c>
@@ -8304,7 +8311,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="57" t="s">
         <v>123</v>
       </c>
@@ -8354,7 +8361,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="57" t="s">
         <v>124</v>
       </c>
@@ -8405,7 +8412,7 @@
       </c>
       <c r="P50" s="43"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="57" t="s">
         <v>123</v>
       </c>
@@ -8456,7 +8463,7 @@
       </c>
       <c r="P51" s="43"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="57" t="s">
         <v>125</v>
       </c>
@@ -8509,7 +8516,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="57" t="s">
         <v>125</v>
       </c>
@@ -8558,7 +8565,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="57" t="s">
         <v>125</v>
       </c>
@@ -8608,7 +8615,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="57" t="s">
         <v>123</v>
       </c>
@@ -8659,7 +8666,7 @@
       </c>
       <c r="Q55" s="59"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="57" t="s">
         <v>124</v>
       </c>
@@ -8711,7 +8718,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="57" t="s">
         <v>123</v>
       </c>
@@ -8761,7 +8768,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="57" t="s">
         <v>125</v>
       </c>
@@ -8811,7 +8818,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="57" t="s">
         <v>125</v>
       </c>
@@ -8864,7 +8871,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="57" t="s">
         <v>125</v>
       </c>
@@ -8917,7 +8924,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="57" t="s">
         <v>123</v>
       </c>
@@ -8967,7 +8974,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="57" t="s">
         <v>124</v>
       </c>
@@ -9017,7 +9024,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="57" t="s">
         <v>123</v>
       </c>
@@ -9067,7 +9074,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="57" t="s">
         <v>125</v>
       </c>
@@ -9119,7 +9126,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="57" t="s">
         <v>125</v>
       </c>
@@ -9166,7 +9173,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="57" t="s">
         <v>125</v>
       </c>
@@ -9216,7 +9223,7 @@
         <v>0.48000000000000026</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="57" t="s">
         <v>123</v>
       </c>
@@ -9266,7 +9273,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="149" t="s">
         <v>124</v>
       </c>
@@ -9313,7 +9320,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="57" t="s">
         <v>123</v>
       </c>
@@ -9363,7 +9370,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="57" t="s">
         <v>125</v>
       </c>
@@ -9412,7 +9419,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="57" t="s">
         <v>125</v>
       </c>
@@ -9465,7 +9472,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="57" t="s">
         <v>125</v>
       </c>
@@ -9515,7 +9522,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="57" t="s">
         <v>126</v>
       </c>
@@ -9565,7 +9572,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="57" t="s">
         <v>123</v>
       </c>
@@ -9615,7 +9622,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="57" t="s">
         <v>125</v>
       </c>
@@ -9665,7 +9672,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="57" t="s">
         <v>125</v>
       </c>
@@ -9717,7 +9724,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="57" t="s">
         <v>125</v>
       </c>
@@ -9766,7 +9773,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="57" t="s">
         <v>126</v>
       </c>
@@ -9816,7 +9823,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="57" t="s">
         <v>123</v>
       </c>
@@ -9865,7 +9872,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="57" t="s">
         <v>125</v>
       </c>
@@ -9912,7 +9919,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="57" t="s">
         <v>125</v>
       </c>
@@ -9964,7 +9971,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="57" t="s">
         <v>125</v>
       </c>
@@ -10017,7 +10024,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="57" t="s">
         <v>126</v>
       </c>
@@ -10067,7 +10074,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="57" t="s">
         <v>123</v>
       </c>
@@ -10117,7 +10124,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="57" t="s">
         <v>125</v>
       </c>
@@ -10167,7 +10174,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="57" t="s">
         <v>125</v>
       </c>
@@ -10217,7 +10224,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="114" t="s">
         <v>125</v>
       </c>
@@ -10265,7 +10272,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="114"/>
       <c r="B88" s="35"/>
       <c r="C88" s="35" t="s">
@@ -10313,7 +10320,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="114"/>
       <c r="B89" s="35"/>
       <c r="C89" s="35" t="s">
@@ -10361,7 +10368,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="114"/>
       <c r="B90" s="35"/>
       <c r="C90" s="35" t="s">
@@ -10409,7 +10416,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="114"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35" t="s">
@@ -10457,7 +10464,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="114"/>
       <c r="B92" s="35"/>
       <c r="C92" s="222" t="s">
@@ -10508,7 +10515,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="114"/>
       <c r="B93" s="35"/>
       <c r="C93" s="35" t="s">
@@ -10556,7 +10563,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="114"/>
       <c r="B94" s="35"/>
       <c r="C94" s="35" t="s">
@@ -10604,7 +10611,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="114"/>
       <c r="B95" s="35"/>
       <c r="C95" s="35" t="s">
@@ -10652,7 +10659,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="114"/>
       <c r="B96" s="35"/>
       <c r="C96" s="35" t="s">
@@ -10699,7 +10706,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="114"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35" t="s">
@@ -10744,7 +10751,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="114"/>
       <c r="B98" s="35"/>
       <c r="C98" s="35" t="s">
@@ -10792,7 +10799,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="114"/>
       <c r="B99" s="35"/>
       <c r="C99" s="35" t="s">
@@ -10840,7 +10847,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="114"/>
       <c r="B100" s="35"/>
       <c r="C100" s="35" t="s">
@@ -10888,7 +10895,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="114"/>
       <c r="B101" s="35"/>
       <c r="C101" s="35" t="s">
@@ -10936,7 +10943,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="114"/>
       <c r="B102" s="35"/>
       <c r="C102" s="35" t="s">
@@ -10984,7 +10991,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="114"/>
       <c r="B103" s="35"/>
       <c r="C103" s="206" t="s">
@@ -11032,7 +11039,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="114"/>
       <c r="B104" s="35"/>
       <c r="C104" s="35" t="s">
@@ -11080,7 +11087,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="114"/>
       <c r="B105" s="35"/>
       <c r="C105" s="35" t="s">
@@ -11128,7 +11135,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="114"/>
       <c r="B106" s="35"/>
       <c r="C106" s="35" t="s">
@@ -11175,7 +11182,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="114"/>
       <c r="B107" s="35"/>
       <c r="C107" s="35" t="s">
@@ -11223,7 +11230,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="114"/>
       <c r="B108" s="35"/>
       <c r="C108" s="35" t="s">
@@ -11271,7 +11278,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="114"/>
       <c r="B109" s="35"/>
       <c r="C109" s="35" t="s">
@@ -11319,7 +11326,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="114"/>
       <c r="B110" s="35"/>
       <c r="C110" s="35" t="s">
@@ -11367,7 +11374,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="114"/>
       <c r="B111" s="35"/>
       <c r="C111" s="206" t="s">
@@ -11415,7 +11422,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="114"/>
       <c r="B112" s="35"/>
       <c r="C112" s="35" t="s">
@@ -11463,7 +11470,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="114"/>
       <c r="B113" s="35"/>
       <c r="C113" s="35" t="s">
@@ -11511,7 +11518,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="114"/>
       <c r="B114" s="35"/>
       <c r="C114" s="35" t="s">
@@ -11559,7 +11566,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="114"/>
       <c r="B115" s="35"/>
       <c r="C115" s="35" t="s">
@@ -11607,7 +11614,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="114"/>
       <c r="B116" s="35"/>
       <c r="C116" s="35" t="s">
@@ -11654,7 +11661,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="114"/>
       <c r="B117" s="35"/>
       <c r="C117" s="35" t="s">
@@ -11699,7 +11706,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="114"/>
       <c r="B118" s="35"/>
       <c r="C118" s="35" t="s">
@@ -11750,7 +11757,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="135"/>
       <c r="B119" s="35"/>
       <c r="C119" s="35" t="s">
@@ -11798,7 +11805,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="135"/>
       <c r="B120" s="35"/>
       <c r="C120" s="35" t="s">
@@ -11846,7 +11853,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="135"/>
       <c r="B121" s="35"/>
       <c r="C121" s="196" t="s">
@@ -11893,7 +11900,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="135"/>
       <c r="B122" s="35"/>
       <c r="C122" s="35" t="s">
@@ -11941,7 +11948,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="135"/>
       <c r="B123" s="35"/>
       <c r="C123" s="35" t="s">
@@ -11989,7 +11996,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="135"/>
       <c r="B124" s="35"/>
       <c r="C124" s="35" t="s">
@@ -12034,7 +12041,7 @@
         <v>1.0600000000000007</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="135"/>
       <c r="B125" s="35"/>
       <c r="C125" s="35" t="s">
@@ -12079,7 +12086,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="135"/>
       <c r="B126" s="35"/>
       <c r="C126" s="206" t="s">
@@ -12127,7 +12134,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="135"/>
       <c r="B127" s="35"/>
       <c r="C127" s="35" t="s">
@@ -12175,7 +12182,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="135"/>
       <c r="B128" s="35"/>
       <c r="C128" s="35" t="s">
@@ -12223,7 +12230,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="135"/>
       <c r="B129" s="35"/>
       <c r="C129" s="35" t="s">
@@ -12271,7 +12278,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="135" t="s">
         <v>26</v>
       </c>
@@ -12321,7 +12328,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="135" t="s">
         <v>26</v>
       </c>
@@ -12371,7 +12378,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="53" t="s">
         <v>26</v>
       </c>
@@ -12389,7 +12396,7 @@
       <c r="M132" s="5"/>
       <c r="N132" s="8"/>
     </row>
-    <row r="133" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="27"/>
       <c r="B133" s="27"/>
       <c r="C133" s="27"/>
@@ -12430,41 +12437,41 @@
       </c>
       <c r="P133" s="59"/>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K134" s="61">
         <f>K133-L1</f>
         <v>1338773.6948400009</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C135" s="261"/>
-      <c r="D135" s="261"/>
-      <c r="E135" s="261"/>
-      <c r="F135" s="261"/>
-      <c r="G135" s="261"/>
-      <c r="H135" s="261"/>
-      <c r="I135" s="261"/>
-      <c r="J135" s="261"/>
-      <c r="K135" s="261"/>
-      <c r="L135" s="261"/>
-      <c r="M135" s="261"/>
-      <c r="N135" s="261"/>
-    </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C136" s="261"/>
-      <c r="D136" s="261"/>
-      <c r="E136" s="261"/>
-      <c r="F136" s="261"/>
-      <c r="G136" s="261"/>
-      <c r="H136" s="261"/>
-      <c r="I136" s="261"/>
-      <c r="J136" s="261"/>
-      <c r="K136" s="261"/>
-      <c r="L136" s="261"/>
-      <c r="M136" s="261"/>
-      <c r="N136" s="261"/>
-    </row>
-    <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C135" s="265"/>
+      <c r="D135" s="265"/>
+      <c r="E135" s="265"/>
+      <c r="F135" s="265"/>
+      <c r="G135" s="265"/>
+      <c r="H135" s="265"/>
+      <c r="I135" s="265"/>
+      <c r="J135" s="265"/>
+      <c r="K135" s="265"/>
+      <c r="L135" s="265"/>
+      <c r="M135" s="265"/>
+      <c r="N135" s="265"/>
+    </row>
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C136" s="265"/>
+      <c r="D136" s="265"/>
+      <c r="E136" s="265"/>
+      <c r="F136" s="265"/>
+      <c r="G136" s="265"/>
+      <c r="H136" s="265"/>
+      <c r="I136" s="265"/>
+      <c r="J136" s="265"/>
+      <c r="K136" s="265"/>
+      <c r="L136" s="265"/>
+      <c r="M136" s="265"/>
+      <c r="N136" s="265"/>
+    </row>
+    <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="79"/>
       <c r="D137" s="79"/>
       <c r="E137" s="79"/>
@@ -12478,121 +12485,121 @@
       <c r="M137" s="79"/>
       <c r="N137" s="79"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C138" s="261" t="s">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C138" s="265" t="s">
         <v>265</v>
       </c>
-      <c r="D138" s="261"/>
-      <c r="E138" s="261"/>
-      <c r="F138" s="261"/>
-      <c r="G138" s="261"/>
-      <c r="H138" s="261"/>
-      <c r="I138" s="261"/>
-      <c r="J138" s="261"/>
-      <c r="K138" s="261"/>
-      <c r="L138" s="261"/>
-      <c r="M138" s="261"/>
-      <c r="N138" s="261"/>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C139" s="261"/>
-      <c r="D139" s="261"/>
-      <c r="E139" s="261"/>
-      <c r="F139" s="261"/>
-      <c r="G139" s="261"/>
-      <c r="H139" s="261"/>
-      <c r="I139" s="261"/>
-      <c r="J139" s="261"/>
-      <c r="K139" s="261"/>
-      <c r="L139" s="261"/>
-      <c r="M139" s="261"/>
-      <c r="N139" s="261"/>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C140" s="261"/>
-      <c r="D140" s="261"/>
-      <c r="E140" s="261"/>
-      <c r="F140" s="261"/>
-      <c r="G140" s="261"/>
-      <c r="H140" s="261"/>
-      <c r="I140" s="261"/>
-      <c r="J140" s="261"/>
-      <c r="K140" s="261"/>
-      <c r="L140" s="261"/>
-      <c r="M140" s="261"/>
-      <c r="N140" s="261"/>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C141" s="261"/>
-      <c r="D141" s="261"/>
-      <c r="E141" s="261"/>
-      <c r="F141" s="261"/>
-      <c r="G141" s="261"/>
-      <c r="H141" s="261"/>
-      <c r="I141" s="261"/>
-      <c r="J141" s="261"/>
-      <c r="K141" s="261"/>
-      <c r="L141" s="261"/>
-      <c r="M141" s="261"/>
-      <c r="N141" s="261"/>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C142" s="261"/>
-      <c r="D142" s="261"/>
-      <c r="E142" s="261"/>
-      <c r="F142" s="261"/>
-      <c r="G142" s="261"/>
-      <c r="H142" s="261"/>
-      <c r="I142" s="261"/>
-      <c r="J142" s="261"/>
-      <c r="K142" s="261"/>
-      <c r="L142" s="261"/>
-      <c r="M142" s="261"/>
-      <c r="N142" s="261"/>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C143" s="261"/>
-      <c r="D143" s="261"/>
-      <c r="E143" s="261"/>
-      <c r="F143" s="261"/>
-      <c r="G143" s="261"/>
-      <c r="H143" s="261"/>
-      <c r="I143" s="261"/>
-      <c r="J143" s="261"/>
-      <c r="K143" s="261"/>
-      <c r="L143" s="261"/>
-      <c r="M143" s="261"/>
-      <c r="N143" s="261"/>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C144" s="261"/>
-      <c r="D144" s="261"/>
-      <c r="E144" s="261"/>
-      <c r="F144" s="261"/>
-      <c r="G144" s="261"/>
-      <c r="H144" s="261"/>
-      <c r="I144" s="261"/>
-      <c r="J144" s="261"/>
-      <c r="K144" s="261"/>
-      <c r="L144" s="261"/>
-      <c r="M144" s="261"/>
-      <c r="N144" s="261"/>
-    </row>
-    <row r="145" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C145" s="261"/>
-      <c r="D145" s="261"/>
-      <c r="E145" s="261"/>
-      <c r="F145" s="261"/>
-      <c r="G145" s="261"/>
-      <c r="H145" s="261"/>
-      <c r="I145" s="261"/>
-      <c r="J145" s="261"/>
-      <c r="K145" s="261"/>
-      <c r="L145" s="261"/>
-      <c r="M145" s="261"/>
-      <c r="N145" s="261"/>
-    </row>
-    <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D138" s="265"/>
+      <c r="E138" s="265"/>
+      <c r="F138" s="265"/>
+      <c r="G138" s="265"/>
+      <c r="H138" s="265"/>
+      <c r="I138" s="265"/>
+      <c r="J138" s="265"/>
+      <c r="K138" s="265"/>
+      <c r="L138" s="265"/>
+      <c r="M138" s="265"/>
+      <c r="N138" s="265"/>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C139" s="265"/>
+      <c r="D139" s="265"/>
+      <c r="E139" s="265"/>
+      <c r="F139" s="265"/>
+      <c r="G139" s="265"/>
+      <c r="H139" s="265"/>
+      <c r="I139" s="265"/>
+      <c r="J139" s="265"/>
+      <c r="K139" s="265"/>
+      <c r="L139" s="265"/>
+      <c r="M139" s="265"/>
+      <c r="N139" s="265"/>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C140" s="265"/>
+      <c r="D140" s="265"/>
+      <c r="E140" s="265"/>
+      <c r="F140" s="265"/>
+      <c r="G140" s="265"/>
+      <c r="H140" s="265"/>
+      <c r="I140" s="265"/>
+      <c r="J140" s="265"/>
+      <c r="K140" s="265"/>
+      <c r="L140" s="265"/>
+      <c r="M140" s="265"/>
+      <c r="N140" s="265"/>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C141" s="265"/>
+      <c r="D141" s="265"/>
+      <c r="E141" s="265"/>
+      <c r="F141" s="265"/>
+      <c r="G141" s="265"/>
+      <c r="H141" s="265"/>
+      <c r="I141" s="265"/>
+      <c r="J141" s="265"/>
+      <c r="K141" s="265"/>
+      <c r="L141" s="265"/>
+      <c r="M141" s="265"/>
+      <c r="N141" s="265"/>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C142" s="265"/>
+      <c r="D142" s="265"/>
+      <c r="E142" s="265"/>
+      <c r="F142" s="265"/>
+      <c r="G142" s="265"/>
+      <c r="H142" s="265"/>
+      <c r="I142" s="265"/>
+      <c r="J142" s="265"/>
+      <c r="K142" s="265"/>
+      <c r="L142" s="265"/>
+      <c r="M142" s="265"/>
+      <c r="N142" s="265"/>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C143" s="265"/>
+      <c r="D143" s="265"/>
+      <c r="E143" s="265"/>
+      <c r="F143" s="265"/>
+      <c r="G143" s="265"/>
+      <c r="H143" s="265"/>
+      <c r="I143" s="265"/>
+      <c r="J143" s="265"/>
+      <c r="K143" s="265"/>
+      <c r="L143" s="265"/>
+      <c r="M143" s="265"/>
+      <c r="N143" s="265"/>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C144" s="265"/>
+      <c r="D144" s="265"/>
+      <c r="E144" s="265"/>
+      <c r="F144" s="265"/>
+      <c r="G144" s="265"/>
+      <c r="H144" s="265"/>
+      <c r="I144" s="265"/>
+      <c r="J144" s="265"/>
+      <c r="K144" s="265"/>
+      <c r="L144" s="265"/>
+      <c r="M144" s="265"/>
+      <c r="N144" s="265"/>
+    </row>
+    <row r="145" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C145" s="265"/>
+      <c r="D145" s="265"/>
+      <c r="E145" s="265"/>
+      <c r="F145" s="265"/>
+      <c r="G145" s="265"/>
+      <c r="H145" s="265"/>
+      <c r="I145" s="265"/>
+      <c r="J145" s="265"/>
+      <c r="K145" s="265"/>
+      <c r="L145" s="265"/>
+      <c r="M145" s="265"/>
+      <c r="N145" s="265"/>
+    </row>
+    <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="79"/>
       <c r="D146" s="79"/>
       <c r="E146" s="79"/>
@@ -12606,7 +12613,7 @@
       <c r="M146" s="79"/>
       <c r="N146" s="79"/>
     </row>
-    <row r="147" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C147" s="79"/>
       <c r="D147" s="79"/>
       <c r="E147" s="79"/>
@@ -12620,112 +12627,118 @@
       <c r="M147" s="79"/>
       <c r="N147" s="79"/>
     </row>
-    <row r="148" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C148" s="260" t="s">
+    <row r="148" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C148" s="264" t="s">
         <v>264</v>
       </c>
-      <c r="D148" s="260"/>
-      <c r="E148" s="260"/>
-      <c r="F148" s="260"/>
-      <c r="G148" s="260"/>
-      <c r="H148" s="260"/>
-      <c r="I148" s="260"/>
-      <c r="J148" s="260"/>
-      <c r="K148" s="260"/>
-      <c r="L148" s="260"/>
-      <c r="M148" s="260"/>
-      <c r="N148" s="260"/>
-    </row>
-    <row r="149" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C149" s="260"/>
-      <c r="D149" s="260"/>
-      <c r="E149" s="260"/>
-      <c r="F149" s="260"/>
-      <c r="G149" s="260"/>
-      <c r="H149" s="260"/>
-      <c r="I149" s="260"/>
-      <c r="J149" s="260"/>
-      <c r="K149" s="260"/>
-      <c r="L149" s="260"/>
-      <c r="M149" s="260"/>
-      <c r="N149" s="260"/>
-    </row>
-    <row r="150" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C150" s="260"/>
-      <c r="D150" s="260"/>
-      <c r="E150" s="260"/>
-      <c r="F150" s="260"/>
-      <c r="G150" s="260"/>
-      <c r="H150" s="260"/>
-      <c r="I150" s="260"/>
-      <c r="J150" s="260"/>
-      <c r="K150" s="260"/>
-      <c r="L150" s="260"/>
-      <c r="M150" s="260"/>
-      <c r="N150" s="260"/>
+      <c r="D148" s="264"/>
+      <c r="E148" s="264"/>
+      <c r="F148" s="264"/>
+      <c r="G148" s="264"/>
+      <c r="H148" s="264"/>
+      <c r="I148" s="264"/>
+      <c r="J148" s="264"/>
+      <c r="K148" s="264"/>
+      <c r="L148" s="264"/>
+      <c r="M148" s="264"/>
+      <c r="N148" s="264"/>
+    </row>
+    <row r="149" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C149" s="264"/>
+      <c r="D149" s="264"/>
+      <c r="E149" s="264"/>
+      <c r="F149" s="264"/>
+      <c r="G149" s="264"/>
+      <c r="H149" s="264"/>
+      <c r="I149" s="264"/>
+      <c r="J149" s="264"/>
+      <c r="K149" s="264"/>
+      <c r="L149" s="264"/>
+      <c r="M149" s="264"/>
+      <c r="N149" s="264"/>
+    </row>
+    <row r="150" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C150" s="264"/>
+      <c r="D150" s="264"/>
+      <c r="E150" s="264"/>
+      <c r="F150" s="264"/>
+      <c r="G150" s="264"/>
+      <c r="H150" s="264"/>
+      <c r="I150" s="264"/>
+      <c r="J150" s="264"/>
+      <c r="K150" s="264"/>
+      <c r="L150" s="264"/>
+      <c r="M150" s="264"/>
+      <c r="N150" s="264"/>
       <c r="P150" s="86">
         <f>L1-K133</f>
         <v>-1338773.6948400009</v>
       </c>
     </row>
-    <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C151" s="260"/>
-      <c r="D151" s="260"/>
-      <c r="E151" s="260"/>
-      <c r="F151" s="260"/>
-      <c r="G151" s="260"/>
-      <c r="H151" s="260"/>
-      <c r="I151" s="260"/>
-      <c r="J151" s="260"/>
-      <c r="K151" s="260"/>
-      <c r="L151" s="260"/>
-      <c r="M151" s="260"/>
-      <c r="N151" s="260"/>
-    </row>
-    <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C152" s="260"/>
-      <c r="D152" s="260"/>
-      <c r="E152" s="260"/>
-      <c r="F152" s="260"/>
-      <c r="G152" s="260"/>
-      <c r="H152" s="260"/>
-      <c r="I152" s="260"/>
-      <c r="J152" s="260"/>
-      <c r="K152" s="260"/>
-      <c r="L152" s="260"/>
-      <c r="M152" s="260"/>
-      <c r="N152" s="260"/>
-    </row>
-    <row r="153" spans="3:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="260"/>
-      <c r="D153" s="260"/>
-      <c r="E153" s="260"/>
-      <c r="F153" s="260"/>
-      <c r="G153" s="260"/>
-      <c r="H153" s="260"/>
-      <c r="I153" s="260"/>
-      <c r="J153" s="260"/>
-      <c r="K153" s="260"/>
-      <c r="L153" s="260"/>
-      <c r="M153" s="260"/>
-      <c r="N153" s="260"/>
-    </row>
-    <row r="154" spans="3:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="260"/>
-      <c r="D154" s="260"/>
-      <c r="E154" s="260"/>
-      <c r="F154" s="260"/>
-      <c r="G154" s="260"/>
-      <c r="H154" s="260"/>
-      <c r="I154" s="260"/>
-      <c r="J154" s="260"/>
-      <c r="K154" s="260"/>
-      <c r="L154" s="260"/>
-      <c r="M154" s="260"/>
-      <c r="N154" s="260"/>
+    <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C151" s="264"/>
+      <c r="D151" s="264"/>
+      <c r="E151" s="264"/>
+      <c r="F151" s="264"/>
+      <c r="G151" s="264"/>
+      <c r="H151" s="264"/>
+      <c r="I151" s="264"/>
+      <c r="J151" s="264"/>
+      <c r="K151" s="264"/>
+      <c r="L151" s="264"/>
+      <c r="M151" s="264"/>
+      <c r="N151" s="264"/>
+    </row>
+    <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C152" s="264"/>
+      <c r="D152" s="264"/>
+      <c r="E152" s="264"/>
+      <c r="F152" s="264"/>
+      <c r="G152" s="264"/>
+      <c r="H152" s="264"/>
+      <c r="I152" s="264"/>
+      <c r="J152" s="264"/>
+      <c r="K152" s="264"/>
+      <c r="L152" s="264"/>
+      <c r="M152" s="264"/>
+      <c r="N152" s="264"/>
+    </row>
+    <row r="153" spans="3:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C153" s="264"/>
+      <c r="D153" s="264"/>
+      <c r="E153" s="264"/>
+      <c r="F153" s="264"/>
+      <c r="G153" s="264"/>
+      <c r="H153" s="264"/>
+      <c r="I153" s="264"/>
+      <c r="J153" s="264"/>
+      <c r="K153" s="264"/>
+      <c r="L153" s="264"/>
+      <c r="M153" s="264"/>
+      <c r="N153" s="264"/>
+    </row>
+    <row r="154" spans="3:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C154" s="264"/>
+      <c r="D154" s="264"/>
+      <c r="E154" s="264"/>
+      <c r="F154" s="264"/>
+      <c r="G154" s="264"/>
+      <c r="H154" s="264"/>
+      <c r="I154" s="264"/>
+      <c r="J154" s="264"/>
+      <c r="K154" s="264"/>
+      <c r="L154" s="264"/>
+      <c r="M154" s="264"/>
+      <c r="N154" s="264"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
     <mergeCell ref="Q14:R15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:N154"/>
@@ -12741,12 +12754,6 @@
     <mergeCell ref="N11:N12"/>
     <mergeCell ref="C5:N8"/>
     <mergeCell ref="C9:N10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12758,9 +12765,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
   <dimension ref="B4:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="240" t="s">
         <v>357</v>
       </c>
@@ -12778,34 +12785,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0166F049-50A4-4ACA-9F6E-1C2F2AD24458}">
   <dimension ref="A2:J27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.5546875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11.5703125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C3" s="287" t="str">
+    <row r="2" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C3" s="294" t="str">
         <f>RESUMEN!C5</f>
         <v>PERÍODO: OCTUBRE</v>
       </c>
-      <c r="D3" s="288"/>
-      <c r="E3" s="288"/>
-      <c r="F3" s="288" t="str">
+      <c r="D3" s="295"/>
+      <c r="E3" s="295"/>
+      <c r="F3" s="295" t="str">
         <f>[1]RESUMEN!A22</f>
         <v xml:space="preserve">Sueldo encargada Sonia Arzamendia Galeano </v>
       </c>
-      <c r="G3" s="288"/>
-      <c r="H3" s="288"/>
-      <c r="I3" s="288"/>
-      <c r="J3" s="289"/>
-    </row>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="G3" s="295"/>
+      <c r="H3" s="295"/>
+      <c r="I3" s="295"/>
+      <c r="J3" s="296"/>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C4" s="1"/>
-      <c r="J4" s="290"/>
-    </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="J4" s="241"/>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="str">
         <f>RESUMEN!A26</f>
         <v xml:space="preserve">Haberes </v>
@@ -12814,13 +12821,13 @@
         <f>RESUMEN!D26</f>
         <v>1026046</v>
       </c>
-      <c r="H5" s="291" t="s">
+      <c r="H5" s="297" t="s">
         <v>358</v>
       </c>
-      <c r="I5" s="291"/>
-      <c r="J5" s="292"/>
-    </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I5" s="297"/>
+      <c r="J5" s="298"/>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="str">
         <f>RESUMEN!A27</f>
         <v>Plus pileta</v>
@@ -12829,13 +12836,13 @@
         <f>RESUMEN!D27</f>
         <v>35809.699999999997</v>
       </c>
-      <c r="H6" s="291" t="s">
+      <c r="H6" s="297" t="s">
         <v>359</v>
       </c>
-      <c r="I6" s="291"/>
-      <c r="J6" s="292"/>
-    </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I6" s="297"/>
+      <c r="J6" s="298"/>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C7" s="1" t="str">
         <f>RESUMEN!A28</f>
         <v>Plus retiro de basura</v>
@@ -12844,11 +12851,11 @@
         <f>RESUMEN!D28</f>
         <v>124792</v>
       </c>
-      <c r="H7" s="291"/>
-      <c r="I7" s="291"/>
-      <c r="J7" s="292"/>
-    </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="H7" s="297"/>
+      <c r="I7" s="297"/>
+      <c r="J7" s="298"/>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C8" s="1" t="str">
         <f>RESUMEN!A29</f>
         <v>Plus cochera</v>
@@ -12857,9 +12864,9 @@
         <f>RESUMEN!D29</f>
         <v>21286.799999999999</v>
       </c>
-      <c r="J8" s="290"/>
-    </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="J8" s="241"/>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9" s="1" t="str">
         <f>RESUMEN!A30</f>
         <v>Adicional Viaticos</v>
@@ -12868,13 +12875,13 @@
         <f>RESUMEN!D30</f>
         <v>59852.7</v>
       </c>
-      <c r="H9" s="291" t="s">
+      <c r="H9" s="297" t="s">
         <v>360</v>
       </c>
-      <c r="I9" s="291"/>
-      <c r="J9" s="292"/>
-    </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I9" s="297"/>
+      <c r="J9" s="298"/>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C10" s="1" t="str">
         <f>RESUMEN!A31</f>
         <v>Adicional remuneracion</v>
@@ -12883,72 +12890,72 @@
         <f>RESUMEN!D31</f>
         <v>50000</v>
       </c>
-      <c r="H10" s="291" t="s">
+      <c r="H10" s="297" t="s">
         <v>359</v>
       </c>
-      <c r="I10" s="291"/>
-      <c r="J10" s="292"/>
-    </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I10" s="297"/>
+      <c r="J10" s="298"/>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C11" s="1"/>
-      <c r="H11" s="291"/>
-      <c r="I11" s="291"/>
-      <c r="J11" s="292"/>
-    </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="293" t="s">
+      <c r="H11" s="297"/>
+      <c r="I11" s="297"/>
+      <c r="J11" s="298"/>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C12" s="244" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="294">
+      <c r="G12" s="245">
         <f>SUM(G5:G11)</f>
         <v>1317787.2</v>
       </c>
-      <c r="J12" s="290"/>
-    </row>
-    <row r="13" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="295"/>
-      <c r="D13" s="296"/>
-      <c r="E13" s="296"/>
-      <c r="F13" s="296"/>
-      <c r="G13" s="296"/>
-      <c r="H13" s="296"/>
-      <c r="I13" s="296"/>
-      <c r="J13" s="297"/>
-    </row>
-    <row r="15" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="287" t="str">
+      <c r="J12" s="241"/>
+    </row>
+    <row r="13" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="246"/>
+      <c r="D13" s="247"/>
+      <c r="E13" s="247"/>
+      <c r="F13" s="247"/>
+      <c r="G13" s="247"/>
+      <c r="H13" s="247"/>
+      <c r="I13" s="247"/>
+      <c r="J13" s="248"/>
+    </row>
+    <row r="15" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C16" s="294" t="str">
         <f>C3</f>
         <v>PERÍODO: OCTUBRE</v>
       </c>
-      <c r="D16" s="288"/>
-      <c r="E16" s="288"/>
-      <c r="F16" s="288" t="str">
+      <c r="D16" s="295"/>
+      <c r="E16" s="295"/>
+      <c r="F16" s="295" t="str">
         <f>[1]RESUMEN!A30</f>
         <v>Sueldo encargada Miriam</v>
       </c>
-      <c r="G16" s="288"/>
-      <c r="H16" s="288"/>
-      <c r="I16" s="288"/>
-      <c r="J16" s="289"/>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="G16" s="295"/>
+      <c r="H16" s="295"/>
+      <c r="I16" s="295"/>
+      <c r="J16" s="296"/>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C17" s="1"/>
-      <c r="J17" s="290"/>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="J17" s="241"/>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" s="1"/>
       <c r="G18" s="43"/>
-      <c r="H18" s="291" t="s">
+      <c r="H18" s="297" t="s">
         <v>358</v>
       </c>
-      <c r="I18" s="291"/>
-      <c r="J18" s="292"/>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I18" s="297"/>
+      <c r="J18" s="298"/>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" s="1" t="str">
         <f>RESUMEN!A34</f>
         <v xml:space="preserve">Haberes </v>
@@ -12957,13 +12964,13 @@
         <f>RESUMEN!D34</f>
         <v>513023</v>
       </c>
-      <c r="H19" s="291" t="s">
+      <c r="H19" s="297" t="s">
         <v>359</v>
       </c>
-      <c r="I19" s="291"/>
-      <c r="J19" s="292"/>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I19" s="297"/>
+      <c r="J19" s="298"/>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="str">
         <f>RESUMEN!A35</f>
         <v>Horas extras</v>
@@ -12972,11 +12979,11 @@
         <f>RESUMEN!D35</f>
         <v>0</v>
       </c>
-      <c r="H20" s="291"/>
-      <c r="I20" s="291"/>
-      <c r="J20" s="292"/>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="H20" s="297"/>
+      <c r="I20" s="297"/>
+      <c r="J20" s="298"/>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" s="1" t="str">
         <f>RESUMEN!A36</f>
         <v>Plus pileta</v>
@@ -12985,9 +12992,9 @@
         <f>RESUMEN!D36</f>
         <v>35809.699999999997</v>
       </c>
-      <c r="J21" s="290"/>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="J21" s="241"/>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C22" s="1" t="str">
         <f>RESUMEN!A37</f>
         <v>Plus retiro de basura</v>
@@ -12996,13 +13003,13 @@
         <f>RESUMEN!D37</f>
         <v>124792</v>
       </c>
-      <c r="H22" s="291" t="s">
+      <c r="H22" s="297" t="s">
         <v>360</v>
       </c>
-      <c r="I22" s="291"/>
-      <c r="J22" s="292"/>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I22" s="297"/>
+      <c r="J22" s="298"/>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C23" s="1" t="str">
         <f>RESUMEN!A38</f>
         <v>Plus cochera</v>
@@ -13011,13 +13018,13 @@
         <f>RESUMEN!D38</f>
         <v>21286.799999999999</v>
       </c>
-      <c r="H23" s="291" t="s">
+      <c r="H23" s="297" t="s">
         <v>359</v>
       </c>
-      <c r="I23" s="291"/>
-      <c r="J23" s="292"/>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I23" s="297"/>
+      <c r="J23" s="298"/>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C24" s="1" t="str">
         <f>RESUMEN!A39</f>
         <v>Adicional Viaticos</v>
@@ -13026,11 +13033,11 @@
         <f>RESUMEN!D39</f>
         <v>59852.7</v>
       </c>
-      <c r="H24" s="291"/>
-      <c r="I24" s="291"/>
-      <c r="J24" s="292"/>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="H24" s="297"/>
+      <c r="I24" s="297"/>
+      <c r="J24" s="298"/>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C25" s="1" t="str">
         <f>RESUMEN!A40</f>
         <v>Adicional remuneracion</v>
@@ -13039,40 +13046,35 @@
         <f>RESUMEN!D40</f>
         <v>50000</v>
       </c>
-      <c r="H25" s="298"/>
-      <c r="I25" s="298"/>
-      <c r="J25" s="299"/>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="293" t="s">
+      <c r="H25" s="242"/>
+      <c r="I25" s="242"/>
+      <c r="J25" s="243"/>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C26" s="244" t="s">
         <v>17</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="294">
+      <c r="G26" s="245">
         <f>SUM(G18:G25)</f>
         <v>804764.2</v>
       </c>
-      <c r="J26" s="290"/>
-    </row>
-    <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C27" s="295"/>
-      <c r="D27" s="296"/>
-      <c r="E27" s="296"/>
-      <c r="F27" s="296"/>
-      <c r="G27" s="296"/>
-      <c r="H27" s="296"/>
-      <c r="I27" s="296"/>
-      <c r="J27" s="297"/>
+      <c r="J26" s="241"/>
+    </row>
+    <row r="27" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C27" s="246"/>
+      <c r="D27" s="247"/>
+      <c r="E27" s="247"/>
+      <c r="F27" s="247"/>
+      <c r="G27" s="247"/>
+      <c r="H27" s="247"/>
+      <c r="I27" s="247"/>
+      <c r="J27" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J20"/>
-    <mergeCell ref="H22:J22"/>
     <mergeCell ref="H23:J24"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F3:J3"/>
@@ -13080,6 +13082,11 @@
     <mergeCell ref="H6:J7"/>
     <mergeCell ref="H9:J9"/>
     <mergeCell ref="H10:J11"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J20"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -13089,18 +13096,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A8B3D07-243A-48F3-942B-AB44D486DEC8}">
   <dimension ref="C4:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C4" s="286" t="s">
+    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C4" s="299" t="s">
         <v>287</v>
       </c>
-      <c r="D4" s="286"/>
-    </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D4" s="299"/>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" s="145">
         <v>52141.08</v>
       </c>
@@ -13108,7 +13115,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" s="145">
         <v>67140.100000000006</v>
       </c>
@@ -13116,7 +13123,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" s="145">
         <v>52121.11</v>
       </c>
@@ -13124,7 +13131,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" s="145">
         <v>67885.119999999995</v>
       </c>
@@ -13132,7 +13139,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" s="145">
         <v>67140.160000000003</v>
       </c>
@@ -13140,7 +13147,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" s="145">
         <v>62141.17</v>
       </c>
@@ -13148,7 +13155,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" s="145">
         <v>67855.179999999993</v>
       </c>
@@ -13156,7 +13163,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" s="145">
         <v>62141.23</v>
       </c>
@@ -13164,7 +13171,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" s="145">
         <v>67855.240000000005</v>
       </c>
@@ -13172,7 +13179,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" s="145">
         <f>SUM(C5:C13)</f>
         <v>566420.39</v>
